--- a/research/traditional_assets/database/data/brazil/brazil_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/brazil/brazil_computers_peripherals.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.141470217799043</v>
+        <v>0.1410189190585263</v>
       </c>
       <c r="C2">
-        <v>301.934365209961</v>
+        <v>299.4432936661264</v>
       </c>
       <c r="D2">
-        <v>224.134365209961</v>
+        <v>225.0762936661264</v>
       </c>
       <c r="E2">
-        <v>-226.5</v>
+        <v>-223.067</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.433</v>
       </c>
       <c r="G2">
         <v>77.8</v>
@@ -1576,28 +1576,28 @@
         <v>110.15</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1726799</v>
       </c>
       <c r="N2">
-        <v>110.15</v>
+        <v>109.9773201</v>
       </c>
       <c r="O2">
-        <v>37.45100000000001</v>
+        <v>37.39228883400001</v>
       </c>
       <c r="P2">
-        <v>72.699</v>
+        <v>72.58503126599999</v>
       </c>
       <c r="Q2">
-        <v>71.29899999999999</v>
+        <v>71.18503126599998</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.141470217799043</v>
+        <v>0.1421080192510366</v>
       </c>
       <c r="T2">
-        <v>1.246903653332528</v>
+        <v>1.255216344354744</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>637.8854748004834</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1410189190585263</v>
+        <v>0.1405676203180095</v>
       </c>
       <c r="C3">
-        <v>299.4432936661264</v>
+        <v>296.960172474279</v>
       </c>
       <c r="D3">
-        <v>225.0762936661264</v>
+        <v>226.026172474279</v>
       </c>
       <c r="E3">
-        <v>-223.067</v>
+        <v>-219.634</v>
       </c>
       <c r="F3">
-        <v>3.433</v>
+        <v>6.866000000000001</v>
       </c>
       <c r="G3">
         <v>77.8</v>
@@ -1658,28 +1658,28 @@
         <v>110.15</v>
       </c>
       <c r="M3">
-        <v>0.1726799</v>
+        <v>0.3453598</v>
       </c>
       <c r="N3">
-        <v>109.9773201</v>
+        <v>109.8046402</v>
       </c>
       <c r="O3">
-        <v>37.39228883400001</v>
+        <v>37.333577668</v>
       </c>
       <c r="P3">
-        <v>72.58503126599999</v>
+        <v>72.471062532</v>
       </c>
       <c r="Q3">
-        <v>71.18503126599998</v>
+        <v>71.071062532</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1421080192510366</v>
+        <v>0.1427588370591934</v>
       </c>
       <c r="T3">
-        <v>1.255216344354744</v>
+        <v>1.263698682132517</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>637.8854748004834</v>
+        <v>318.9427374002418</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1405676203180095</v>
+        <v>0.1401163215774928</v>
       </c>
       <c r="C4">
-        <v>296.960172474279</v>
+        <v>294.4851027184995</v>
       </c>
       <c r="D4">
-        <v>226.026172474279</v>
+        <v>226.9841027184995</v>
       </c>
       <c r="E4">
-        <v>-219.634</v>
+        <v>-216.201</v>
       </c>
       <c r="F4">
-        <v>6.866000000000001</v>
+        <v>10.299</v>
       </c>
       <c r="G4">
         <v>77.8</v>
@@ -1740,28 +1740,28 @@
         <v>110.15</v>
       </c>
       <c r="M4">
-        <v>0.3453598</v>
+        <v>0.5180397</v>
       </c>
       <c r="N4">
-        <v>109.8046402</v>
+        <v>109.6319603</v>
       </c>
       <c r="O4">
-        <v>37.333577668</v>
+        <v>37.274866502</v>
       </c>
       <c r="P4">
-        <v>72.471062532</v>
+        <v>72.35709379799999</v>
       </c>
       <c r="Q4">
-        <v>71.071062532</v>
+        <v>70.95709379799999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1427588370591934</v>
+        <v>0.1434230737912297</v>
       </c>
       <c r="T4">
-        <v>1.263698682132517</v>
+        <v>1.272355913472717</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>318.9427374002418</v>
+        <v>212.6284916001612</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1401163215774928</v>
+        <v>0.1396650228369761</v>
       </c>
       <c r="C5">
-        <v>294.4851027184995</v>
+        <v>292.0181872037955</v>
       </c>
       <c r="D5">
-        <v>226.9841027184995</v>
+        <v>227.9501872037956</v>
       </c>
       <c r="E5">
-        <v>-216.201</v>
+        <v>-212.768</v>
       </c>
       <c r="F5">
-        <v>10.299</v>
+        <v>13.732</v>
       </c>
       <c r="G5">
         <v>77.8</v>
@@ -1822,28 +1822,28 @@
         <v>110.15</v>
       </c>
       <c r="M5">
-        <v>0.5180397</v>
+        <v>0.6907196</v>
       </c>
       <c r="N5">
-        <v>109.6319603</v>
+        <v>109.4592804</v>
       </c>
       <c r="O5">
-        <v>37.274866502</v>
+        <v>37.21615533600001</v>
       </c>
       <c r="P5">
-        <v>72.35709379799999</v>
+        <v>72.243125064</v>
       </c>
       <c r="Q5">
-        <v>70.95709379799999</v>
+        <v>70.84312506399999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1434230737912297</v>
+        <v>0.1441011487885167</v>
       </c>
       <c r="T5">
-        <v>1.272355913472717</v>
+        <v>1.281193503799172</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>212.6284916001612</v>
+        <v>159.4713687001209</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1396650228369761</v>
+        <v>0.1392137240964593</v>
       </c>
       <c r="C6">
-        <v>292.0181872037955</v>
+        <v>289.559530492881</v>
       </c>
       <c r="D6">
-        <v>227.9501872037956</v>
+        <v>228.924530492881</v>
       </c>
       <c r="E6">
-        <v>-212.768</v>
+        <v>-209.335</v>
       </c>
       <c r="F6">
-        <v>13.732</v>
+        <v>17.165</v>
       </c>
       <c r="G6">
         <v>77.8</v>
@@ -1904,28 +1904,28 @@
         <v>110.15</v>
       </c>
       <c r="M6">
-        <v>0.6907196</v>
+        <v>0.8633995000000001</v>
       </c>
       <c r="N6">
-        <v>109.4592804</v>
+        <v>109.2866005</v>
       </c>
       <c r="O6">
-        <v>37.21615533600001</v>
+        <v>37.15744417000001</v>
       </c>
       <c r="P6">
-        <v>72.243125064</v>
+        <v>72.12915633</v>
       </c>
       <c r="Q6">
-        <v>70.84312506399999</v>
+        <v>70.72915633</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1441011487885167</v>
+        <v>0.1447934990489045</v>
       </c>
       <c r="T6">
-        <v>1.281193503799172</v>
+        <v>1.290217148658815</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>159.4713687001209</v>
+        <v>127.5770949600967</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1392137240964593</v>
+        <v>0.1387624253559425</v>
       </c>
       <c r="C7">
-        <v>289.559530492881</v>
+        <v>287.1092389439028</v>
       </c>
       <c r="D7">
-        <v>228.924530492881</v>
+        <v>229.9072389439028</v>
       </c>
       <c r="E7">
-        <v>-209.335</v>
+        <v>-205.902</v>
       </c>
       <c r="F7">
-        <v>17.165</v>
+        <v>20.598</v>
       </c>
       <c r="G7">
         <v>77.8</v>
@@ -1986,28 +1986,28 @@
         <v>110.15</v>
       </c>
       <c r="M7">
-        <v>0.8633995000000001</v>
+        <v>1.0360794</v>
       </c>
       <c r="N7">
-        <v>109.2866005</v>
+        <v>109.1139206</v>
       </c>
       <c r="O7">
-        <v>37.15744417000001</v>
+        <v>37.098733004</v>
       </c>
       <c r="P7">
-        <v>72.12915633</v>
+        <v>72.015187596</v>
       </c>
       <c r="Q7">
-        <v>70.72915633</v>
+        <v>70.615187596</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1447934990489045</v>
+        <v>0.1455005801658963</v>
       </c>
       <c r="T7">
-        <v>1.290217148658815</v>
+        <v>1.299432785962281</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>127.5770949600967</v>
+        <v>106.3142458000806</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1387624253559425</v>
+        <v>0.1383111266154258</v>
       </c>
       <c r="C8">
-        <v>287.1092389439028</v>
+        <v>284.6674207491432</v>
       </c>
       <c r="D8">
-        <v>229.9072389439028</v>
+        <v>230.8984207491432</v>
       </c>
       <c r="E8">
-        <v>-205.902</v>
+        <v>-202.469</v>
       </c>
       <c r="F8">
-        <v>20.598</v>
+        <v>24.031</v>
       </c>
       <c r="G8">
         <v>77.8</v>
@@ -2068,28 +2068,28 @@
         <v>110.15</v>
       </c>
       <c r="M8">
-        <v>1.0360794</v>
+        <v>1.2087593</v>
       </c>
       <c r="N8">
-        <v>109.1139206</v>
+        <v>108.9412407</v>
       </c>
       <c r="O8">
-        <v>37.098733004</v>
+        <v>37.04002183800001</v>
       </c>
       <c r="P8">
-        <v>72.015187596</v>
+        <v>71.90121886200001</v>
       </c>
       <c r="Q8">
-        <v>70.615187596</v>
+        <v>70.501218862</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1455005801658963</v>
+        <v>0.1462228673284148</v>
       </c>
       <c r="T8">
-        <v>1.299432785962281</v>
+        <v>1.308846609014208</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>106.3142458000806</v>
+        <v>91.12649640006907</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1383111266154259</v>
+        <v>0.1378598278749091</v>
       </c>
       <c r="C9">
-        <v>284.6674207491431</v>
+        <v>282.2341859747283</v>
       </c>
       <c r="D9">
-        <v>230.8984207491431</v>
+        <v>231.8981859747284</v>
       </c>
       <c r="E9">
-        <v>-202.469</v>
+        <v>-199.036</v>
       </c>
       <c r="F9">
-        <v>24.031</v>
+        <v>27.464</v>
       </c>
       <c r="G9">
         <v>77.8</v>
@@ -2150,28 +2150,28 @@
         <v>110.15</v>
       </c>
       <c r="M9">
-        <v>1.2087593</v>
+        <v>1.3814392</v>
       </c>
       <c r="N9">
-        <v>108.9412407</v>
+        <v>108.7685608</v>
       </c>
       <c r="O9">
-        <v>37.04002183800001</v>
+        <v>36.98131067200001</v>
       </c>
       <c r="P9">
-        <v>71.90121886200001</v>
+        <v>71.787250128</v>
       </c>
       <c r="Q9">
-        <v>70.501218862</v>
+        <v>70.38725012799999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1462228673284149</v>
+        <v>0.1469608563857707</v>
       </c>
       <c r="T9">
-        <v>1.308846609014208</v>
+        <v>1.318465080393351</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>91.12649640006906</v>
+        <v>79.73568435006044</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1378598278749091</v>
+        <v>0.1374085291343923</v>
       </c>
       <c r="C10">
-        <v>282.2341859747283</v>
+        <v>279.809646601372</v>
       </c>
       <c r="D10">
-        <v>231.8981859747284</v>
+        <v>232.906646601372</v>
       </c>
       <c r="E10">
-        <v>-199.036</v>
+        <v>-195.603</v>
       </c>
       <c r="F10">
-        <v>27.464</v>
+        <v>30.897</v>
       </c>
       <c r="G10">
         <v>77.8</v>
@@ -2232,28 +2232,28 @@
         <v>110.15</v>
       </c>
       <c r="M10">
-        <v>1.3814392</v>
+        <v>1.5541191</v>
       </c>
       <c r="N10">
-        <v>108.7685608</v>
+        <v>108.5958809</v>
       </c>
       <c r="O10">
-        <v>36.98131067200001</v>
+        <v>36.922599506</v>
       </c>
       <c r="P10">
-        <v>71.787250128</v>
+        <v>71.67328139400001</v>
       </c>
       <c r="Q10">
-        <v>70.38725012799999</v>
+        <v>70.27328139400001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1469608563857707</v>
+        <v>0.1477150649828487</v>
       </c>
       <c r="T10">
-        <v>1.318465080393351</v>
+        <v>1.32829494674786</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>79.73568435006044</v>
+        <v>70.87616386672039</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1374085291343923</v>
+        <v>0.1369572303938756</v>
       </c>
       <c r="C11">
-        <v>279.809646601372</v>
+        <v>277.3939165661874</v>
       </c>
       <c r="D11">
-        <v>232.906646601372</v>
+        <v>233.9239165661874</v>
       </c>
       <c r="E11">
-        <v>-195.603</v>
+        <v>-192.17</v>
       </c>
       <c r="F11">
-        <v>30.897</v>
+        <v>34.33</v>
       </c>
       <c r="G11">
         <v>77.8</v>
@@ -2314,28 +2314,28 @@
         <v>110.15</v>
       </c>
       <c r="M11">
-        <v>1.5541191</v>
+        <v>1.726799</v>
       </c>
       <c r="N11">
-        <v>108.5958809</v>
+        <v>108.423201</v>
       </c>
       <c r="O11">
-        <v>36.922599506</v>
+        <v>36.86388834</v>
       </c>
       <c r="P11">
-        <v>71.67328139400001</v>
+        <v>71.55931266</v>
       </c>
       <c r="Q11">
-        <v>70.27328139400001</v>
+        <v>70.15931266</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1477150649828487</v>
+        <v>0.1484860337709729</v>
       </c>
       <c r="T11">
-        <v>1.32829494674786</v>
+        <v>1.338343254576913</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>70.87616386672039</v>
+        <v>63.78854748004836</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1369572303938756</v>
+        <v>0.1365059316533588</v>
       </c>
       <c r="C12">
-        <v>277.3939165661874</v>
+        <v>274.9871118056</v>
       </c>
       <c r="D12">
-        <v>233.9239165661874</v>
+        <v>234.9501118056</v>
       </c>
       <c r="E12">
-        <v>-192.17</v>
+        <v>-188.737</v>
       </c>
       <c r="F12">
-        <v>34.33000000000001</v>
+        <v>37.763</v>
       </c>
       <c r="G12">
         <v>77.8</v>
@@ -2396,28 +2396,28 @@
         <v>110.15</v>
       </c>
       <c r="M12">
-        <v>1.726799</v>
+        <v>1.8994789</v>
       </c>
       <c r="N12">
-        <v>108.423201</v>
+        <v>108.2505211</v>
       </c>
       <c r="O12">
-        <v>36.86388834</v>
+        <v>36.805177174</v>
       </c>
       <c r="P12">
-        <v>71.55931266</v>
+        <v>71.44534392599999</v>
       </c>
       <c r="Q12">
-        <v>70.15931266</v>
+        <v>70.04534392599999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1484860337709729</v>
+        <v>0.1492743277004032</v>
       </c>
       <c r="T12">
-        <v>1.338343254576913</v>
+        <v>1.348617367076282</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>63.78854748004834</v>
+        <v>57.98958861822577</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1365059316533588</v>
+        <v>0.1360546329128421</v>
       </c>
       <c r="C13">
-        <v>274.9871118056</v>
+        <v>272.5893502993937</v>
       </c>
       <c r="D13">
-        <v>234.9501118056</v>
+        <v>235.9853502993937</v>
       </c>
       <c r="E13">
-        <v>-188.737</v>
+        <v>-185.304</v>
       </c>
       <c r="F13">
-        <v>37.763</v>
+        <v>41.196</v>
       </c>
       <c r="G13">
         <v>77.8</v>
@@ -2478,28 +2478,28 @@
         <v>110.15</v>
       </c>
       <c r="M13">
-        <v>1.8994789</v>
+        <v>2.0721588</v>
       </c>
       <c r="N13">
-        <v>108.2505211</v>
+        <v>108.0778412</v>
       </c>
       <c r="O13">
-        <v>36.805177174</v>
+        <v>36.74646600800001</v>
       </c>
       <c r="P13">
-        <v>71.44534392599999</v>
+        <v>71.331375192</v>
       </c>
       <c r="Q13">
-        <v>70.04534392599999</v>
+        <v>69.93137519199999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1492743277004032</v>
+        <v>0.1500805374009569</v>
       </c>
       <c r="T13">
-        <v>1.348617367076282</v>
+        <v>1.359124982132455</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>57.98958861822577</v>
+        <v>53.15712290004029</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1360546329128421</v>
+        <v>0.1356033341723254</v>
       </c>
       <c r="C14">
-        <v>272.5893502993937</v>
+        <v>270.2007521159284</v>
       </c>
       <c r="D14">
-        <v>235.9853502993937</v>
+        <v>237.0297521159284</v>
       </c>
       <c r="E14">
-        <v>-185.304</v>
+        <v>-181.871</v>
       </c>
       <c r="F14">
-        <v>41.196</v>
+        <v>44.629</v>
       </c>
       <c r="G14">
         <v>77.8</v>
@@ -2560,28 +2560,28 @@
         <v>110.15</v>
       </c>
       <c r="M14">
-        <v>2.0721588</v>
+        <v>2.2448387</v>
       </c>
       <c r="N14">
-        <v>108.0778412</v>
+        <v>107.9051613</v>
       </c>
       <c r="O14">
-        <v>36.74646600800001</v>
+        <v>36.687754842</v>
       </c>
       <c r="P14">
-        <v>71.331375192</v>
+        <v>71.217406458</v>
       </c>
       <c r="Q14">
-        <v>69.93137519199999</v>
+        <v>69.81740645799999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1500805374009569</v>
+        <v>0.1509052806578452</v>
       </c>
       <c r="T14">
-        <v>1.359124982132455</v>
+        <v>1.369874151557736</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>53.15712290004029</v>
+        <v>49.06811344619103</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1356033341723254</v>
+        <v>0.1351520354318086</v>
       </c>
       <c r="C15">
-        <v>270.2007521159284</v>
+        <v>267.8214394585619</v>
       </c>
       <c r="D15">
-        <v>237.0297521159284</v>
+        <v>238.0834394585619</v>
       </c>
       <c r="E15">
-        <v>-181.871</v>
+        <v>-178.438</v>
       </c>
       <c r="F15">
-        <v>44.629</v>
+        <v>48.062</v>
       </c>
       <c r="G15">
         <v>77.8</v>
@@ -2642,28 +2642,28 @@
         <v>110.15</v>
       </c>
       <c r="M15">
-        <v>2.2448387</v>
+        <v>2.4175186</v>
       </c>
       <c r="N15">
-        <v>107.9051613</v>
+        <v>107.7324814</v>
       </c>
       <c r="O15">
-        <v>36.687754842</v>
+        <v>36.62904367600001</v>
       </c>
       <c r="P15">
-        <v>71.217406458</v>
+        <v>71.103437724</v>
       </c>
       <c r="Q15">
-        <v>69.81740645799999</v>
+        <v>69.703437724</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1509052806578452</v>
+        <v>0.1517492039904751</v>
       </c>
       <c r="T15">
-        <v>1.369874151557736</v>
+        <v>1.380873301667324</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>49.06811344619103</v>
+        <v>45.56324820003454</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1351520354318086</v>
+        <v>0.1347007366912918</v>
       </c>
       <c r="C16">
-        <v>267.8214394585619</v>
+        <v>265.4515367133156</v>
       </c>
       <c r="D16">
-        <v>238.0834394585619</v>
+        <v>239.1465367133157</v>
       </c>
       <c r="E16">
-        <v>-178.438</v>
+        <v>-175.005</v>
       </c>
       <c r="F16">
-        <v>48.062</v>
+        <v>51.49500000000001</v>
       </c>
       <c r="G16">
         <v>77.8</v>
@@ -2724,28 +2724,28 @@
         <v>110.15</v>
       </c>
       <c r="M16">
-        <v>2.4175186</v>
+        <v>2.590198500000001</v>
       </c>
       <c r="N16">
-        <v>107.7324814</v>
+        <v>107.5598015</v>
       </c>
       <c r="O16">
-        <v>36.62904367600001</v>
+        <v>36.57033251000001</v>
       </c>
       <c r="P16">
-        <v>71.103437724</v>
+        <v>70.98946899000001</v>
       </c>
       <c r="Q16">
-        <v>69.703437724</v>
+        <v>69.58946899</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1517492039904751</v>
+        <v>0.1526129843426963</v>
       </c>
       <c r="T16">
-        <v>1.380873301667324</v>
+        <v>1.392131255308904</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2762,7 +2762,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>45.56324820003454</v>
+        <v>42.52569832003223</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1347007366912918</v>
+        <v>0.1342494379507751</v>
       </c>
       <c r="C17">
-        <v>265.4515367133156</v>
+        <v>263.0911704978252</v>
       </c>
       <c r="D17">
-        <v>239.1465367133157</v>
+        <v>240.2191704978252</v>
       </c>
       <c r="E17">
-        <v>-175.005</v>
+        <v>-171.572</v>
       </c>
       <c r="F17">
-        <v>51.495</v>
+        <v>54.928</v>
       </c>
       <c r="G17">
         <v>77.8</v>
@@ -2806,28 +2806,28 @@
         <v>110.15</v>
       </c>
       <c r="M17">
-        <v>2.5901985</v>
+        <v>2.7628784</v>
       </c>
       <c r="N17">
-        <v>107.5598015</v>
+        <v>107.3871216</v>
       </c>
       <c r="O17">
-        <v>36.57033251000001</v>
+        <v>36.51162134400001</v>
       </c>
       <c r="P17">
-        <v>70.98946899000001</v>
+        <v>70.875500256</v>
       </c>
       <c r="Q17">
-        <v>69.58946899</v>
+        <v>69.47550025599999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1526129843426963</v>
+        <v>0.1534973308937799</v>
       </c>
       <c r="T17">
-        <v>1.392131255308904</v>
+        <v>1.403657255465759</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>42.52569832003224</v>
+        <v>39.86784217503021</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1342494379507751</v>
+        <v>0.1337981392102583</v>
       </c>
       <c r="C18">
-        <v>263.0911704978252</v>
+        <v>260.7404697116112</v>
       </c>
       <c r="D18">
-        <v>240.2191704978252</v>
+        <v>241.3014697116112</v>
       </c>
       <c r="E18">
-        <v>-171.572</v>
+        <v>-168.139</v>
       </c>
       <c r="F18">
-        <v>54.928</v>
+        <v>58.361</v>
       </c>
       <c r="G18">
         <v>77.8</v>
@@ -2888,28 +2888,28 @@
         <v>110.15</v>
       </c>
       <c r="M18">
-        <v>2.7628784</v>
+        <v>2.9355583</v>
       </c>
       <c r="N18">
-        <v>107.3871216</v>
+        <v>107.2144417</v>
       </c>
       <c r="O18">
-        <v>36.51162134400001</v>
+        <v>36.452910178</v>
       </c>
       <c r="P18">
-        <v>70.875500256</v>
+        <v>70.76153152200001</v>
       </c>
       <c r="Q18">
-        <v>69.47550025599999</v>
+        <v>69.36153152200001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1534973308937799</v>
+        <v>0.1544029870003113</v>
       </c>
       <c r="T18">
-        <v>1.403657255465759</v>
+        <v>1.415460990566153</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>39.86784217503021</v>
+        <v>37.52267498826373</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1337981392102583</v>
+        <v>0.1333468404697416</v>
       </c>
       <c r="C19">
-        <v>260.7404697116112</v>
+        <v>258.3995655877176</v>
       </c>
       <c r="D19">
-        <v>241.3014697116112</v>
+        <v>242.3935655877176</v>
       </c>
       <c r="E19">
-        <v>-168.139</v>
+        <v>-164.706</v>
       </c>
       <c r="F19">
-        <v>58.361</v>
+        <v>61.79400000000001</v>
       </c>
       <c r="G19">
         <v>77.8</v>
@@ -2970,28 +2970,28 @@
         <v>110.15</v>
       </c>
       <c r="M19">
-        <v>2.9355583</v>
+        <v>3.108238200000001</v>
       </c>
       <c r="N19">
-        <v>107.2144417</v>
+        <v>107.0417618</v>
       </c>
       <c r="O19">
-        <v>36.452910178</v>
+        <v>36.394199012</v>
       </c>
       <c r="P19">
-        <v>70.76153152200001</v>
+        <v>70.647562788</v>
       </c>
       <c r="Q19">
-        <v>69.36153152200001</v>
+        <v>69.247562788</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1544029870003113</v>
+        <v>0.1553307322801727</v>
       </c>
       <c r="T19">
-        <v>1.415460990566153</v>
+        <v>1.427552621644606</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>37.52267498826373</v>
+        <v>35.43808193336019</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1333468404697416</v>
+        <v>0.1328955417292249</v>
       </c>
       <c r="C20">
-        <v>258.3995655877176</v>
+        <v>256.0685917457573</v>
       </c>
       <c r="D20">
-        <v>242.3935655877175</v>
+        <v>243.4955917457574</v>
       </c>
       <c r="E20">
-        <v>-164.706</v>
+        <v>-161.273</v>
       </c>
       <c r="F20">
-        <v>61.794</v>
+        <v>65.227</v>
       </c>
       <c r="G20">
         <v>77.8</v>
@@ -3052,28 +3052,28 @@
         <v>110.15</v>
       </c>
       <c r="M20">
-        <v>3.1082382</v>
+        <v>3.2809181</v>
       </c>
       <c r="N20">
-        <v>107.0417618</v>
+        <v>106.8690819</v>
       </c>
       <c r="O20">
-        <v>36.394199012</v>
+        <v>36.33548784600001</v>
       </c>
       <c r="P20">
-        <v>70.647562788</v>
+        <v>70.53359405400001</v>
       </c>
       <c r="Q20">
-        <v>69.247562788</v>
+        <v>69.133594054</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1553307322801727</v>
+        <v>0.1562813848508949</v>
       </c>
       <c r="T20">
-        <v>1.427552621644606</v>
+        <v>1.439942811515119</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>35.43808193336019</v>
+        <v>33.57291972634123</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1328955417292249</v>
+        <v>0.1324442429887081</v>
       </c>
       <c r="C21">
-        <v>256.0685917457573</v>
+        <v>253.7476842464121</v>
       </c>
       <c r="D21">
-        <v>243.4955917457574</v>
+        <v>244.6076842464121</v>
       </c>
       <c r="E21">
-        <v>-161.273</v>
+        <v>-157.84</v>
       </c>
       <c r="F21">
-        <v>65.227</v>
+        <v>68.66000000000001</v>
       </c>
       <c r="G21">
         <v>77.8</v>
@@ -3134,28 +3134,28 @@
         <v>110.15</v>
       </c>
       <c r="M21">
-        <v>3.2809181</v>
+        <v>3.453598</v>
       </c>
       <c r="N21">
-        <v>106.8690819</v>
+        <v>106.696402</v>
       </c>
       <c r="O21">
-        <v>36.33548784600001</v>
+        <v>36.27677668</v>
       </c>
       <c r="P21">
-        <v>70.53359405400001</v>
+        <v>70.41962531999999</v>
       </c>
       <c r="Q21">
-        <v>69.133594054</v>
+        <v>69.01962531999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1562813848508949</v>
+        <v>0.1572558037358852</v>
       </c>
       <c r="T21">
-        <v>1.439942811515119</v>
+        <v>1.452642756132395</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>33.57291972634123</v>
+        <v>31.89427374002417</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1324442429887081</v>
+        <v>0.1319929442481914</v>
       </c>
       <c r="C22">
-        <v>253.7476842464121</v>
+        <v>251.4369816474323</v>
       </c>
       <c r="D22">
-        <v>244.6076842464121</v>
+        <v>245.7299816474323</v>
       </c>
       <c r="E22">
-        <v>-157.84</v>
+        <v>-154.407</v>
       </c>
       <c r="F22">
-        <v>68.66000000000001</v>
+        <v>72.093</v>
       </c>
       <c r="G22">
         <v>77.8</v>
@@ -3216,28 +3216,28 @@
         <v>110.15</v>
       </c>
       <c r="M22">
-        <v>3.453598</v>
+        <v>3.6262779</v>
       </c>
       <c r="N22">
-        <v>106.696402</v>
+        <v>106.5237221</v>
       </c>
       <c r="O22">
-        <v>36.27677668</v>
+        <v>36.218065514</v>
       </c>
       <c r="P22">
-        <v>70.41962531999999</v>
+        <v>70.305656586</v>
       </c>
       <c r="Q22">
-        <v>69.01962531999999</v>
+        <v>68.90565658599999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1572558037358852</v>
+        <v>0.1582548914534068</v>
       </c>
       <c r="T22">
-        <v>1.452642756132395</v>
+        <v>1.465664218334918</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3254,7 +3254,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>31.89427374002417</v>
+        <v>30.37549880002302</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1319929442481914</v>
+        <v>0.1315416455076746</v>
       </c>
       <c r="C23">
-        <v>251.4369816474324</v>
+        <v>249.1366250611859</v>
       </c>
       <c r="D23">
-        <v>245.7299816474324</v>
+        <v>246.8626250611859</v>
       </c>
       <c r="E23">
-        <v>-154.407</v>
+        <v>-150.974</v>
       </c>
       <c r="F23">
-        <v>72.093</v>
+        <v>75.526</v>
       </c>
       <c r="G23">
         <v>77.8</v>
@@ -3298,28 +3298,28 @@
         <v>110.15</v>
       </c>
       <c r="M23">
-        <v>3.6262779</v>
+        <v>3.7989578</v>
       </c>
       <c r="N23">
-        <v>106.5237221</v>
+        <v>106.3510422</v>
       </c>
       <c r="O23">
-        <v>36.218065514</v>
+        <v>36.15935434800001</v>
       </c>
       <c r="P23">
-        <v>70.305656586</v>
+        <v>70.191687852</v>
       </c>
       <c r="Q23">
-        <v>68.90565658599999</v>
+        <v>68.791687852</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1582548914534068</v>
+        <v>0.159279596804711</v>
       </c>
       <c r="T23">
-        <v>1.465664218334918</v>
+        <v>1.479019564183659</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>30.37549880002302</v>
+        <v>28.99479430911289</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1315416455076746</v>
+        <v>0.1310903467671579</v>
       </c>
       <c r="C24">
-        <v>249.1366250611859</v>
+        <v>246.8467582138056</v>
       </c>
       <c r="D24">
-        <v>246.8626250611859</v>
+        <v>248.0057582138056</v>
       </c>
       <c r="E24">
-        <v>-150.974</v>
+        <v>-147.541</v>
       </c>
       <c r="F24">
-        <v>75.526</v>
+        <v>78.959</v>
       </c>
       <c r="G24">
         <v>77.8</v>
@@ -3380,28 +3380,28 @@
         <v>110.15</v>
       </c>
       <c r="M24">
-        <v>3.7989578</v>
+        <v>3.9716377</v>
       </c>
       <c r="N24">
-        <v>106.3510422</v>
+        <v>106.1783623</v>
       </c>
       <c r="O24">
-        <v>36.15935434800001</v>
+        <v>36.10064318200001</v>
       </c>
       <c r="P24">
-        <v>70.191687852</v>
+        <v>70.077719118</v>
       </c>
       <c r="Q24">
-        <v>68.791687852</v>
+        <v>68.677719118</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.159279596804711</v>
+        <v>0.1603309178794258</v>
       </c>
       <c r="T24">
-        <v>1.479019564183659</v>
+        <v>1.492721802132368</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3418,7 +3418,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>28.99479430911289</v>
+        <v>27.73415107828189</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1310903467671579</v>
+        <v>0.1306390480266411</v>
       </c>
       <c r="C25">
-        <v>246.8467582138056</v>
+        <v>244.5675275059882</v>
       </c>
       <c r="D25">
-        <v>248.0057582138056</v>
+        <v>249.1595275059882</v>
       </c>
       <c r="E25">
-        <v>-147.541</v>
+        <v>-144.108</v>
       </c>
       <c r="F25">
-        <v>78.959</v>
+        <v>82.39200000000001</v>
       </c>
       <c r="G25">
         <v>77.8</v>
@@ -3462,28 +3462,28 @@
         <v>110.15</v>
       </c>
       <c r="M25">
-        <v>3.9716377</v>
+        <v>4.1443176</v>
       </c>
       <c r="N25">
-        <v>106.1783623</v>
+        <v>106.0056824</v>
       </c>
       <c r="O25">
-        <v>36.10064318200001</v>
+        <v>36.041932016</v>
       </c>
       <c r="P25">
-        <v>70.077719118</v>
+        <v>69.96375038400001</v>
       </c>
       <c r="Q25">
-        <v>68.677719118</v>
+        <v>68.563750384</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1603309178794258</v>
+        <v>0.161409905298212</v>
       </c>
       <c r="T25">
-        <v>1.492721802132368</v>
+        <v>1.506784625290254</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>27.73415107828189</v>
+        <v>26.57856145002015</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1306390480266411</v>
+        <v>0.1301877492861244</v>
       </c>
       <c r="C26">
-        <v>244.5675275059882</v>
+        <v>242.2990820754974</v>
       </c>
       <c r="D26">
-        <v>249.1595275059882</v>
+        <v>250.3240820754974</v>
       </c>
       <c r="E26">
-        <v>-144.108</v>
+        <v>-140.675</v>
       </c>
       <c r="F26">
-        <v>82.392</v>
+        <v>85.825</v>
       </c>
       <c r="G26">
         <v>77.8</v>
@@ -3544,28 +3544,28 @@
         <v>110.15</v>
       </c>
       <c r="M26">
-        <v>4.1443176</v>
+        <v>4.3169975</v>
       </c>
       <c r="N26">
-        <v>106.0056824</v>
+        <v>105.8330025</v>
       </c>
       <c r="O26">
-        <v>36.041932016</v>
+        <v>35.98322085</v>
       </c>
       <c r="P26">
-        <v>69.96375038400001</v>
+        <v>69.84978165000001</v>
       </c>
       <c r="Q26">
-        <v>68.563750384</v>
+        <v>68.44978165000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.161409905298212</v>
+        <v>0.1625176657148325</v>
       </c>
       <c r="T26">
-        <v>1.506784625290254</v>
+        <v>1.521222457065684</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3582,7 +3582,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>26.57856145002015</v>
+        <v>25.51541899201934</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1301877492861244</v>
+        <v>0.1297364505456076</v>
       </c>
       <c r="C27">
-        <v>242.2990820754974</v>
+        <v>240.0415738614292</v>
       </c>
       <c r="D27">
-        <v>250.3240820754974</v>
+        <v>251.4995738614292</v>
       </c>
       <c r="E27">
-        <v>-140.675</v>
+        <v>-137.242</v>
       </c>
       <c r="F27">
-        <v>85.825</v>
+        <v>89.25800000000001</v>
       </c>
       <c r="G27">
         <v>77.8</v>
@@ -3626,28 +3626,28 @@
         <v>110.15</v>
       </c>
       <c r="M27">
-        <v>4.3169975</v>
+        <v>4.489677400000001</v>
       </c>
       <c r="N27">
-        <v>105.8330025</v>
+        <v>105.6603226</v>
       </c>
       <c r="O27">
-        <v>35.98322085</v>
+        <v>35.924509684</v>
       </c>
       <c r="P27">
-        <v>69.84978165000001</v>
+        <v>69.735812916</v>
       </c>
       <c r="Q27">
-        <v>68.44978165000001</v>
+        <v>68.33581291599999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1625176657148325</v>
+        <v>0.1636553656021725</v>
       </c>
       <c r="T27">
-        <v>1.521222457065684</v>
+        <v>1.536050500510719</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>25.51541899201934</v>
+        <v>24.53405672309551</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1297364505456076</v>
+        <v>0.1292851518050909</v>
       </c>
       <c r="C28">
-        <v>240.0415738614292</v>
+        <v>237.7951576702955</v>
       </c>
       <c r="D28">
-        <v>251.4995738614292</v>
+        <v>252.6861576702956</v>
       </c>
       <c r="E28">
-        <v>-137.242</v>
+        <v>-133.809</v>
       </c>
       <c r="F28">
-        <v>89.25800000000001</v>
+        <v>92.691</v>
       </c>
       <c r="G28">
         <v>77.8</v>
@@ -3708,28 +3708,28 @@
         <v>110.15</v>
       </c>
       <c r="M28">
-        <v>4.489677400000001</v>
+        <v>4.6623573</v>
       </c>
       <c r="N28">
-        <v>105.6603226</v>
+        <v>105.4876427</v>
       </c>
       <c r="O28">
-        <v>35.924509684</v>
+        <v>35.86579851800001</v>
       </c>
       <c r="P28">
-        <v>69.735812916</v>
+        <v>69.621844182</v>
       </c>
       <c r="Q28">
-        <v>68.33581291599999</v>
+        <v>68.221844182</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1636553656021725</v>
+        <v>0.1648242353494395</v>
       </c>
       <c r="T28">
-        <v>1.536050500510719</v>
+        <v>1.551284791721372</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>24.53405672309551</v>
+        <v>23.62538795557346</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1292851518050909</v>
+        <v>0.1288338530645741</v>
       </c>
       <c r="C29">
-        <v>237.7951576702955</v>
+        <v>235.5599912439876</v>
       </c>
       <c r="D29">
-        <v>252.6861576702956</v>
+        <v>253.8839912439876</v>
       </c>
       <c r="E29">
-        <v>-133.809</v>
+        <v>-130.376</v>
       </c>
       <c r="F29">
-        <v>92.691</v>
+        <v>96.12400000000001</v>
       </c>
       <c r="G29">
         <v>77.8</v>
@@ -3790,28 +3790,28 @@
         <v>110.15</v>
       </c>
       <c r="M29">
-        <v>4.6623573</v>
+        <v>4.8350372</v>
       </c>
       <c r="N29">
-        <v>105.4876427</v>
+        <v>105.3149628</v>
       </c>
       <c r="O29">
-        <v>35.86579851800001</v>
+        <v>35.807087352</v>
       </c>
       <c r="P29">
-        <v>69.621844182</v>
+        <v>69.50787544799999</v>
       </c>
       <c r="Q29">
-        <v>68.221844182</v>
+        <v>68.10787544799999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1648242353494395</v>
+        <v>0.1660255737007974</v>
       </c>
       <c r="T29">
-        <v>1.551284791721372</v>
+        <v>1.566942257687876</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>23.62538795557346</v>
+        <v>22.78162410001726</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1288338530645741</v>
+        <v>0.1283825543240574</v>
       </c>
       <c r="C30">
-        <v>235.5599912439876</v>
+        <v>233.3362353296819</v>
       </c>
       <c r="D30">
-        <v>253.8839912439876</v>
+        <v>255.0932353296819</v>
       </c>
       <c r="E30">
-        <v>-130.376</v>
+        <v>-126.943</v>
       </c>
       <c r="F30">
-        <v>96.12400000000001</v>
+        <v>99.55700000000002</v>
       </c>
       <c r="G30">
         <v>77.8</v>
@@ -3872,28 +3872,28 @@
         <v>110.15</v>
       </c>
       <c r="M30">
-        <v>4.8350372</v>
+        <v>5.007717100000001</v>
       </c>
       <c r="N30">
-        <v>105.3149628</v>
+        <v>105.1422829</v>
       </c>
       <c r="O30">
-        <v>35.807087352</v>
+        <v>35.748376186</v>
       </c>
       <c r="P30">
-        <v>69.50787544799999</v>
+        <v>69.393906714</v>
       </c>
       <c r="Q30">
-        <v>68.10787544799999</v>
+        <v>67.99390671399999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1660255737007974</v>
+        <v>0.1672607525690949</v>
       </c>
       <c r="T30">
-        <v>1.566942257687876</v>
+        <v>1.583040779033719</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>22.78162410001726</v>
+        <v>21.99605085518908</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1283825543240574</v>
+        <v>0.1279312555835407</v>
       </c>
       <c r="C31">
-        <v>233.336235329682</v>
+        <v>231.1240537517533</v>
       </c>
       <c r="D31">
-        <v>255.093235329682</v>
+        <v>256.3140537517532</v>
       </c>
       <c r="E31">
-        <v>-126.943</v>
+        <v>-123.51</v>
       </c>
       <c r="F31">
-        <v>99.557</v>
+        <v>102.99</v>
       </c>
       <c r="G31">
         <v>77.8</v>
@@ -3954,28 +3954,28 @@
         <v>110.15</v>
       </c>
       <c r="M31">
-        <v>5.0077171</v>
+        <v>5.180396999999999</v>
       </c>
       <c r="N31">
-        <v>105.1422829</v>
+        <v>104.969603</v>
       </c>
       <c r="O31">
-        <v>35.74837618600001</v>
+        <v>35.68966502000001</v>
       </c>
       <c r="P31">
-        <v>69.393906714</v>
+        <v>69.27993798</v>
       </c>
       <c r="Q31">
-        <v>67.99390671399999</v>
+        <v>67.87993797999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1672607525690949</v>
+        <v>0.1685312222622009</v>
       </c>
       <c r="T31">
-        <v>1.583040779033719</v>
+        <v>1.5995992581323</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>21.99605085518909</v>
+        <v>21.26284916001612</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1279312555835407</v>
+        <v>0.1274799568430239</v>
       </c>
       <c r="C32">
-        <v>231.1240537517533</v>
+        <v>228.9236134857624</v>
       </c>
       <c r="D32">
-        <v>256.3140537517532</v>
+        <v>257.5466134857624</v>
       </c>
       <c r="E32">
-        <v>-123.51</v>
+        <v>-120.077</v>
       </c>
       <c r="F32">
-        <v>102.99</v>
+        <v>106.423</v>
       </c>
       <c r="G32">
         <v>77.8</v>
@@ -4036,28 +4036,28 @@
         <v>110.15</v>
       </c>
       <c r="M32">
-        <v>5.180396999999999</v>
+        <v>5.3530769</v>
       </c>
       <c r="N32">
-        <v>104.969603</v>
+        <v>104.7969231</v>
       </c>
       <c r="O32">
-        <v>35.68966502000001</v>
+        <v>35.630953854</v>
       </c>
       <c r="P32">
-        <v>69.27993798</v>
+        <v>69.165969246</v>
       </c>
       <c r="Q32">
-        <v>67.87993797999999</v>
+        <v>67.765969246</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1685312222622009</v>
+        <v>0.1698385171638028</v>
       </c>
       <c r="T32">
-        <v>1.5995992581323</v>
+        <v>1.616637693146781</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>21.26284916001612</v>
+        <v>20.5769508000156</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1274799568430239</v>
+        <v>0.1270286581025071</v>
       </c>
       <c r="C33">
-        <v>228.9236134857624</v>
+        <v>226.7350847345897</v>
       </c>
       <c r="D33">
-        <v>257.5466134857624</v>
+        <v>258.7910847345897</v>
       </c>
       <c r="E33">
-        <v>-120.077</v>
+        <v>-116.644</v>
       </c>
       <c r="F33">
-        <v>106.423</v>
+        <v>109.856</v>
       </c>
       <c r="G33">
         <v>77.8</v>
@@ -4118,28 +4118,28 @@
         <v>110.15</v>
       </c>
       <c r="M33">
-        <v>5.3530769</v>
+        <v>5.5257568</v>
       </c>
       <c r="N33">
-        <v>104.7969231</v>
+        <v>104.6242432</v>
       </c>
       <c r="O33">
-        <v>35.630953854</v>
+        <v>35.572242688</v>
       </c>
       <c r="P33">
-        <v>69.165969246</v>
+        <v>69.05200051200001</v>
       </c>
       <c r="Q33">
-        <v>67.765969246</v>
+        <v>67.652000512</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1698385171638028</v>
+        <v>0.1711842619154517</v>
       </c>
       <c r="T33">
-        <v>1.616637693146781</v>
+        <v>1.634177258602865</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4156,7 +4156,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>20.5769508000156</v>
+        <v>19.93392108751511</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1270286581025071</v>
+        <v>0.1265773593619904</v>
       </c>
       <c r="C34">
-        <v>226.7350847345897</v>
+        <v>224.5586410067853</v>
       </c>
       <c r="D34">
-        <v>258.7910847345897</v>
+        <v>260.0476410067853</v>
       </c>
       <c r="E34">
-        <v>-116.644</v>
+        <v>-113.211</v>
       </c>
       <c r="F34">
-        <v>109.856</v>
+        <v>113.289</v>
       </c>
       <c r="G34">
         <v>77.8</v>
@@ -4200,28 +4200,28 @@
         <v>110.15</v>
       </c>
       <c r="M34">
-        <v>5.5257568</v>
+        <v>5.6984367</v>
       </c>
       <c r="N34">
-        <v>104.6242432</v>
+        <v>104.4515633</v>
       </c>
       <c r="O34">
-        <v>35.572242688</v>
+        <v>35.513531522</v>
       </c>
       <c r="P34">
-        <v>69.05200051200001</v>
+        <v>68.93803177800001</v>
       </c>
       <c r="Q34">
-        <v>67.652000512</v>
+        <v>67.538031778</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1711842619154517</v>
+        <v>0.1725701781522245</v>
       </c>
       <c r="T34">
-        <v>1.634177258602865</v>
+        <v>1.652240393177042</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>19.93392108751511</v>
+        <v>19.32986287274192</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1265773593619904</v>
+        <v>0.1261260606214737</v>
       </c>
       <c r="C35">
-        <v>224.5586410067853</v>
+        <v>222.3944591972148</v>
       </c>
       <c r="D35">
-        <v>260.0476410067853</v>
+        <v>261.3164591972148</v>
       </c>
       <c r="E35">
-        <v>-113.211</v>
+        <v>-109.778</v>
       </c>
       <c r="F35">
-        <v>113.289</v>
+        <v>116.722</v>
       </c>
       <c r="G35">
         <v>77.8</v>
@@ -4282,28 +4282,28 @@
         <v>110.15</v>
       </c>
       <c r="M35">
-        <v>5.6984367</v>
+        <v>5.871116600000001</v>
       </c>
       <c r="N35">
-        <v>104.4515633</v>
+        <v>104.2788834</v>
       </c>
       <c r="O35">
-        <v>35.513531522</v>
+        <v>35.45482035600001</v>
       </c>
       <c r="P35">
-        <v>68.93803177800001</v>
+        <v>68.82406304400001</v>
       </c>
       <c r="Q35">
-        <v>67.538031778</v>
+        <v>67.42406304400001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1725701781522245</v>
+        <v>0.1739980918507177</v>
       </c>
       <c r="T35">
-        <v>1.652240393177042</v>
+        <v>1.670850895465587</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>19.32986287274192</v>
+        <v>18.76133749413187</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1261260606214737</v>
+        <v>0.1256747618809569</v>
       </c>
       <c r="C36">
-        <v>222.3944591972148</v>
+        <v>220.2427196700756</v>
       </c>
       <c r="D36">
-        <v>261.3164591972148</v>
+        <v>262.5977196700756</v>
       </c>
       <c r="E36">
-        <v>-109.778</v>
+        <v>-106.345</v>
       </c>
       <c r="F36">
-        <v>116.722</v>
+        <v>120.155</v>
       </c>
       <c r="G36">
         <v>77.8</v>
@@ -4364,28 +4364,28 @@
         <v>110.15</v>
       </c>
       <c r="M36">
-        <v>5.871116600000001</v>
+        <v>6.043796500000001</v>
       </c>
       <c r="N36">
-        <v>104.2788834</v>
+        <v>104.1062035</v>
       </c>
       <c r="O36">
-        <v>35.45482035600001</v>
+        <v>35.39610919</v>
       </c>
       <c r="P36">
-        <v>68.82406304400001</v>
+        <v>68.71009431</v>
       </c>
       <c r="Q36">
-        <v>67.42406304400001</v>
+        <v>67.31009431</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1739980918507177</v>
+        <v>0.1754699413553183</v>
       </c>
       <c r="T36">
-        <v>1.670850895465587</v>
+        <v>1.69003402859378</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>18.76133749413187</v>
+        <v>18.22529928001381</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1256747618809569</v>
+        <v>0.1252234631404402</v>
       </c>
       <c r="C37">
-        <v>220.2427196700756</v>
+        <v>218.1036063443689</v>
       </c>
       <c r="D37">
-        <v>262.5977196700756</v>
+        <v>263.8916063443689</v>
       </c>
       <c r="E37">
-        <v>-106.345</v>
+        <v>-102.912</v>
       </c>
       <c r="F37">
-        <v>120.155</v>
+        <v>123.588</v>
       </c>
       <c r="G37">
         <v>77.8</v>
@@ -4446,28 +4446,28 @@
         <v>110.15</v>
       </c>
       <c r="M37">
-        <v>6.043796500000001</v>
+        <v>6.216476400000001</v>
       </c>
       <c r="N37">
-        <v>104.1062035</v>
+        <v>103.9335236</v>
       </c>
       <c r="O37">
-        <v>35.39610919</v>
+        <v>35.337398024</v>
       </c>
       <c r="P37">
-        <v>68.71009431</v>
+        <v>68.59612557599999</v>
       </c>
       <c r="Q37">
-        <v>67.31009431</v>
+        <v>67.19612557599999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1754699413553183</v>
+        <v>0.1769877861569378</v>
       </c>
       <c r="T37">
-        <v>1.69003402859378</v>
+        <v>1.709816634632229</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>18.22529928001381</v>
+        <v>17.71904096668009</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1252234631404402</v>
+        <v>0.1247721643999234</v>
       </c>
       <c r="C38">
-        <v>218.103606344369</v>
+        <v>215.9773067819103</v>
       </c>
       <c r="D38">
-        <v>263.8916063443689</v>
+        <v>265.1983067819103</v>
       </c>
       <c r="E38">
-        <v>-102.912</v>
+        <v>-99.479</v>
       </c>
       <c r="F38">
-        <v>123.588</v>
+        <v>127.021</v>
       </c>
       <c r="G38">
         <v>77.8</v>
@@ -4528,28 +4528,28 @@
         <v>110.15</v>
       </c>
       <c r="M38">
-        <v>6.216476399999999</v>
+        <v>6.3891563</v>
       </c>
       <c r="N38">
-        <v>103.9335236</v>
+        <v>103.7608437</v>
       </c>
       <c r="O38">
-        <v>35.337398024</v>
+        <v>35.27868685800001</v>
       </c>
       <c r="P38">
-        <v>68.59612557599999</v>
+        <v>68.48215684199999</v>
       </c>
       <c r="Q38">
-        <v>67.19612557599999</v>
+        <v>67.08215684199999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1769877861569377</v>
+        <v>0.178553816507815</v>
       </c>
       <c r="T38">
-        <v>1.709816634632228</v>
+        <v>1.730227259909993</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>17.7190409666801</v>
+        <v>17.24014796758064</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1247721643999234</v>
+        <v>0.1243208656594067</v>
       </c>
       <c r="C39">
-        <v>215.9773067819103</v>
+        <v>213.8640122779685</v>
       </c>
       <c r="D39">
-        <v>265.1983067819103</v>
+        <v>266.5180122779685</v>
       </c>
       <c r="E39">
-        <v>-99.479</v>
+        <v>-96.04599999999999</v>
       </c>
       <c r="F39">
-        <v>127.021</v>
+        <v>130.454</v>
       </c>
       <c r="G39">
         <v>77.8</v>
@@ -4610,28 +4610,28 @@
         <v>110.15</v>
       </c>
       <c r="M39">
-        <v>6.3891563</v>
+        <v>6.5618362</v>
       </c>
       <c r="N39">
-        <v>103.7608437</v>
+        <v>103.5881638</v>
       </c>
       <c r="O39">
-        <v>35.27868685800001</v>
+        <v>35.21997569200001</v>
       </c>
       <c r="P39">
-        <v>68.48215684199999</v>
+        <v>68.368188108</v>
       </c>
       <c r="Q39">
-        <v>67.08215684199999</v>
+        <v>66.96818810799999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.178553816507815</v>
+        <v>0.180170363966785</v>
       </c>
       <c r="T39">
-        <v>1.730227259909993</v>
+        <v>1.751296292454782</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>17.24014796758064</v>
+        <v>16.78645986317062</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1243208656594067</v>
+        <v>0.1238695669188899</v>
       </c>
       <c r="C40">
-        <v>213.8640122779685</v>
+        <v>211.7639179546237</v>
       </c>
       <c r="D40">
-        <v>266.5180122779685</v>
+        <v>267.8509179546236</v>
       </c>
       <c r="E40">
-        <v>-96.04599999999999</v>
+        <v>-92.613</v>
       </c>
       <c r="F40">
-        <v>130.454</v>
+        <v>133.887</v>
       </c>
       <c r="G40">
         <v>77.8</v>
@@ -4692,28 +4692,28 @@
         <v>110.15</v>
       </c>
       <c r="M40">
-        <v>6.5618362</v>
+        <v>6.7345161</v>
       </c>
       <c r="N40">
-        <v>103.5881638</v>
+        <v>103.4154839</v>
       </c>
       <c r="O40">
-        <v>35.21997569200001</v>
+        <v>35.161264526</v>
       </c>
       <c r="P40">
-        <v>68.368188108</v>
+        <v>68.254219374</v>
       </c>
       <c r="Q40">
-        <v>66.96818810799999</v>
+        <v>66.854219374</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.180170363966785</v>
+        <v>0.1818399129817868</v>
       </c>
       <c r="T40">
-        <v>1.751296292454782</v>
+        <v>1.77305611295186</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>16.78645986317062</v>
+        <v>16.35603781539702</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1238695669188899</v>
+        <v>0.1234182681783732</v>
       </c>
       <c r="C41">
-        <v>211.7639179546237</v>
+        <v>209.6772228569415</v>
       </c>
       <c r="D41">
-        <v>267.8509179546236</v>
+        <v>269.1972228569415</v>
       </c>
       <c r="E41">
-        <v>-92.613</v>
+        <v>-89.17999999999998</v>
       </c>
       <c r="F41">
-        <v>133.887</v>
+        <v>137.32</v>
       </c>
       <c r="G41">
         <v>77.8</v>
@@ -4774,28 +4774,28 @@
         <v>110.15</v>
       </c>
       <c r="M41">
-        <v>6.7345161</v>
+        <v>6.907196000000001</v>
       </c>
       <c r="N41">
-        <v>103.4154839</v>
+        <v>103.242804</v>
       </c>
       <c r="O41">
-        <v>35.161264526</v>
+        <v>35.10255336</v>
       </c>
       <c r="P41">
-        <v>68.254219374</v>
+        <v>68.14025064</v>
       </c>
       <c r="Q41">
-        <v>66.854219374</v>
+        <v>66.74025064</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1818399129817868</v>
+        <v>0.183565113630622</v>
       </c>
       <c r="T41">
-        <v>1.77305611295186</v>
+        <v>1.795541260798839</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>16.35603781539702</v>
+        <v>15.94713687001209</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1234182681783732</v>
+        <v>0.1229669694378564</v>
       </c>
       <c r="C42">
-        <v>209.6772228569415</v>
+        <v>207.6041300520619</v>
       </c>
       <c r="D42">
-        <v>269.1972228569415</v>
+        <v>270.557130052062</v>
       </c>
       <c r="E42">
-        <v>-89.17999999999998</v>
+        <v>-85.74699999999999</v>
       </c>
       <c r="F42">
-        <v>137.32</v>
+        <v>140.753</v>
       </c>
       <c r="G42">
         <v>77.8</v>
@@ -4856,28 +4856,28 @@
         <v>110.15</v>
       </c>
       <c r="M42">
-        <v>6.907196000000001</v>
+        <v>7.0798759</v>
       </c>
       <c r="N42">
-        <v>103.242804</v>
+        <v>103.0701241</v>
       </c>
       <c r="O42">
-        <v>35.10255336</v>
+        <v>35.043842194</v>
       </c>
       <c r="P42">
-        <v>68.14025064</v>
+        <v>68.02628190600001</v>
       </c>
       <c r="Q42">
-        <v>66.74025064</v>
+        <v>66.626281906</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.183565113630622</v>
+        <v>0.1853487956573838</v>
       </c>
       <c r="T42">
-        <v>1.795541260798839</v>
+        <v>1.818788617047412</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>15.94713687001209</v>
+        <v>15.55818231220691</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1229669694378564</v>
+        <v>0.1225156706973397</v>
       </c>
       <c r="C43">
-        <v>207.6041300520619</v>
+        <v>205.5448467313074</v>
       </c>
       <c r="D43">
-        <v>270.557130052062</v>
+        <v>271.9308467313074</v>
       </c>
       <c r="E43">
-        <v>-85.74699999999999</v>
+        <v>-82.31399999999999</v>
       </c>
       <c r="F43">
-        <v>140.753</v>
+        <v>144.186</v>
       </c>
       <c r="G43">
         <v>77.8</v>
@@ -4938,28 +4938,28 @@
         <v>110.15</v>
       </c>
       <c r="M43">
-        <v>7.0798759</v>
+        <v>7.2525558</v>
       </c>
       <c r="N43">
-        <v>103.0701241</v>
+        <v>102.8974442</v>
       </c>
       <c r="O43">
-        <v>35.043842194</v>
+        <v>34.985131028</v>
       </c>
       <c r="P43">
-        <v>68.02628190600001</v>
+        <v>67.91231317200001</v>
       </c>
       <c r="Q43">
-        <v>66.626281906</v>
+        <v>66.51231317200001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1853487956573838</v>
+        <v>0.1871939839609305</v>
       </c>
       <c r="T43">
-        <v>1.818788617047412</v>
+        <v>1.842837606270074</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>15.55818231220691</v>
+        <v>15.18774940001151</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1225156706973397</v>
+        <v>0.122064371956823</v>
       </c>
       <c r="C44">
-        <v>205.5448467313073</v>
+        <v>203.4995843154159</v>
       </c>
       <c r="D44">
-        <v>271.9308467313073</v>
+        <v>273.3185843154159</v>
       </c>
       <c r="E44">
-        <v>-82.31399999999999</v>
+        <v>-78.881</v>
       </c>
       <c r="F44">
-        <v>144.186</v>
+        <v>147.619</v>
       </c>
       <c r="G44">
         <v>77.8</v>
@@ -5020,28 +5020,28 @@
         <v>110.15</v>
       </c>
       <c r="M44">
-        <v>7.2525558</v>
+        <v>7.4252357</v>
       </c>
       <c r="N44">
-        <v>102.8974442</v>
+        <v>102.7247643</v>
       </c>
       <c r="O44">
-        <v>34.985131028</v>
+        <v>34.926419862</v>
       </c>
       <c r="P44">
-        <v>67.91231317200001</v>
+        <v>67.798344438</v>
       </c>
       <c r="Q44">
-        <v>66.51231317200001</v>
+        <v>66.398344438</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1871939839609305</v>
+        <v>0.1891039157137245</v>
       </c>
       <c r="T44">
-        <v>1.842837606270073</v>
+        <v>1.867730419675986</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>15.18774940001151</v>
+        <v>14.83454592559264</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.122064371956823</v>
+        <v>0.1216130732163062</v>
       </c>
       <c r="C45">
-        <v>203.4995843154159</v>
+        <v>201.4685585630155</v>
       </c>
       <c r="D45">
-        <v>273.3185843154159</v>
+        <v>274.7205585630155</v>
       </c>
       <c r="E45">
-        <v>-78.881</v>
+        <v>-75.44800000000001</v>
       </c>
       <c r="F45">
-        <v>147.619</v>
+        <v>151.052</v>
       </c>
       <c r="G45">
         <v>77.8</v>
@@ -5102,28 +5102,28 @@
         <v>110.15</v>
       </c>
       <c r="M45">
-        <v>7.4252357</v>
+        <v>7.597915599999999</v>
       </c>
       <c r="N45">
-        <v>102.7247643</v>
+        <v>102.5520844</v>
       </c>
       <c r="O45">
-        <v>34.926419862</v>
+        <v>34.86770869600001</v>
       </c>
       <c r="P45">
-        <v>67.798344438</v>
+        <v>67.684375704</v>
       </c>
       <c r="Q45">
-        <v>66.398344438</v>
+        <v>66.284375704</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1891039157137245</v>
+        <v>0.1910820593148325</v>
       </c>
       <c r="T45">
-        <v>1.867730419675986</v>
+        <v>1.893512262132109</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>14.83454592559264</v>
+        <v>14.49739715455645</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1216130732163062</v>
+        <v>0.1211617744757895</v>
       </c>
       <c r="C46">
-        <v>201.4685585630155</v>
+        <v>199.4519896824511</v>
       </c>
       <c r="D46">
-        <v>274.7205585630155</v>
+        <v>276.1369896824511</v>
       </c>
       <c r="E46">
-        <v>-75.44800000000001</v>
+        <v>-72.01499999999999</v>
       </c>
       <c r="F46">
-        <v>151.052</v>
+        <v>154.485</v>
       </c>
       <c r="G46">
         <v>77.8</v>
@@ -5184,28 +5184,28 @@
         <v>110.15</v>
       </c>
       <c r="M46">
-        <v>7.597915599999999</v>
+        <v>7.770595500000001</v>
       </c>
       <c r="N46">
-        <v>102.5520844</v>
+        <v>102.3794045</v>
       </c>
       <c r="O46">
-        <v>34.86770869600001</v>
+        <v>34.80899753000001</v>
       </c>
       <c r="P46">
-        <v>67.684375704</v>
+        <v>67.57040696999999</v>
       </c>
       <c r="Q46">
-        <v>66.284375704</v>
+        <v>66.17040696999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1910820593148325</v>
+        <v>0.1931321354105263</v>
       </c>
       <c r="T46">
-        <v>1.893512262132109</v>
+        <v>1.920231626132092</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>14.49739715455645</v>
+        <v>14.17523277334408</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1211617744757895</v>
+        <v>0.1207104757352727</v>
       </c>
       <c r="C47">
-        <v>199.4519896824511</v>
+        <v>197.4501024470918</v>
       </c>
       <c r="D47">
-        <v>276.1369896824511</v>
+        <v>277.5681024470918</v>
       </c>
       <c r="E47">
-        <v>-72.01499999999999</v>
+        <v>-68.58199999999999</v>
       </c>
       <c r="F47">
-        <v>154.485</v>
+        <v>157.918</v>
       </c>
       <c r="G47">
         <v>77.8</v>
@@ -5266,28 +5266,28 @@
         <v>110.15</v>
       </c>
       <c r="M47">
-        <v>7.770595500000001</v>
+        <v>7.9432754</v>
       </c>
       <c r="N47">
-        <v>102.3794045</v>
+        <v>102.2067246</v>
       </c>
       <c r="O47">
-        <v>34.80899753000001</v>
+        <v>34.750286364</v>
       </c>
       <c r="P47">
-        <v>67.57040696999999</v>
+        <v>67.456438236</v>
       </c>
       <c r="Q47">
-        <v>66.17040696999999</v>
+        <v>66.05643823599999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1931321354105263</v>
+        <v>0.195258140250505</v>
       </c>
       <c r="T47">
-        <v>1.920231626132092</v>
+        <v>1.947940596206148</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>14.17523277334408</v>
+        <v>13.86707553914095</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1207104757352727</v>
+        <v>0.120259176994756</v>
       </c>
       <c r="C48">
-        <v>197.4501024470918</v>
+        <v>195.4631263142403</v>
       </c>
       <c r="D48">
-        <v>277.5681024470918</v>
+        <v>279.0141263142403</v>
       </c>
       <c r="E48">
-        <v>-68.58199999999999</v>
+        <v>-65.14899999999997</v>
       </c>
       <c r="F48">
-        <v>157.918</v>
+        <v>161.351</v>
       </c>
       <c r="G48">
         <v>77.8</v>
@@ -5348,28 +5348,28 @@
         <v>110.15</v>
       </c>
       <c r="M48">
-        <v>7.9432754</v>
+        <v>8.115955300000001</v>
       </c>
       <c r="N48">
-        <v>102.2067246</v>
+        <v>102.0340447</v>
       </c>
       <c r="O48">
-        <v>34.750286364</v>
+        <v>34.691575198</v>
       </c>
       <c r="P48">
-        <v>67.456438236</v>
+        <v>67.342469502</v>
       </c>
       <c r="Q48">
-        <v>66.05643823599999</v>
+        <v>65.94246950199999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.195258140250505</v>
+        <v>0.1974643716882188</v>
       </c>
       <c r="T48">
-        <v>1.947940596206148</v>
+        <v>1.976695187792433</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>13.86707553914095</v>
+        <v>13.57203137873369</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.120259176994756</v>
+        <v>0.1198078782542392</v>
       </c>
       <c r="C49">
-        <v>195.4631263142403</v>
+        <v>193.4912955477799</v>
       </c>
       <c r="D49">
-        <v>279.0141263142403</v>
+        <v>280.4752955477799</v>
       </c>
       <c r="E49">
-        <v>-65.14899999999997</v>
+        <v>-61.71599999999998</v>
       </c>
       <c r="F49">
-        <v>161.351</v>
+        <v>164.784</v>
       </c>
       <c r="G49">
         <v>77.8</v>
@@ -5430,28 +5430,28 @@
         <v>110.15</v>
       </c>
       <c r="M49">
-        <v>8.115955300000001</v>
+        <v>8.2886352</v>
       </c>
       <c r="N49">
-        <v>102.0340447</v>
+        <v>101.8613648</v>
       </c>
       <c r="O49">
-        <v>34.691575198</v>
+        <v>34.632864032</v>
       </c>
       <c r="P49">
-        <v>67.342469502</v>
+        <v>67.228500768</v>
       </c>
       <c r="Q49">
-        <v>65.94246950199999</v>
+        <v>65.828500768</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1974643716882188</v>
+        <v>0.1997554581812293</v>
       </c>
       <c r="T49">
-        <v>1.976695187792433</v>
+        <v>2.00655572520896</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>13.57203137873369</v>
+        <v>13.28928072501007</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1198078782542392</v>
+        <v>0.1193565795137225</v>
       </c>
       <c r="C50">
-        <v>193.49129554778</v>
+        <v>191.5348493446943</v>
       </c>
       <c r="D50">
-        <v>280.47529554778</v>
+        <v>281.9518493446943</v>
       </c>
       <c r="E50">
-        <v>-61.71600000000001</v>
+        <v>-58.28299999999999</v>
       </c>
       <c r="F50">
-        <v>164.784</v>
+        <v>168.217</v>
       </c>
       <c r="G50">
         <v>77.8</v>
@@ -5512,28 +5512,28 @@
         <v>110.15</v>
       </c>
       <c r="M50">
-        <v>8.2886352</v>
+        <v>8.4613151</v>
       </c>
       <c r="N50">
-        <v>101.8613648</v>
+        <v>101.6886849</v>
       </c>
       <c r="O50">
-        <v>34.632864032</v>
+        <v>34.574152866</v>
       </c>
       <c r="P50">
-        <v>67.228500768</v>
+        <v>67.11453203400001</v>
       </c>
       <c r="Q50">
-        <v>65.828500768</v>
+        <v>65.714532034</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1997554581812292</v>
+        <v>0.2021363912033774</v>
       </c>
       <c r="T50">
-        <v>2.006555725208959</v>
+        <v>2.037587264092801</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>13.28928072501007</v>
+        <v>13.01807091429558</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1193565795137225</v>
+        <v>0.1194002807732057</v>
       </c>
       <c r="C51">
-        <v>191.5348493446943</v>
+        <v>187.9581886041018</v>
       </c>
       <c r="D51">
-        <v>281.9518493446943</v>
+        <v>281.8081886041018</v>
       </c>
       <c r="E51">
-        <v>-58.28299999999999</v>
+        <v>-54.84999999999999</v>
       </c>
       <c r="F51">
-        <v>168.217</v>
+        <v>171.65</v>
       </c>
       <c r="G51">
         <v>77.8</v>
@@ -5594,45 +5594,45 @@
         <v>110.15</v>
       </c>
       <c r="M51">
-        <v>8.4613151</v>
+        <v>8.89147</v>
       </c>
       <c r="N51">
-        <v>101.6886849</v>
+        <v>101.25853</v>
       </c>
       <c r="O51">
-        <v>34.574152866</v>
+        <v>34.4279002</v>
       </c>
       <c r="P51">
-        <v>67.11453203400001</v>
+        <v>66.8306298</v>
       </c>
       <c r="Q51">
-        <v>65.714532034</v>
+        <v>65.43062979999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2021363912033774</v>
+        <v>0.2046125615464114</v>
       </c>
       <c r="T51">
-        <v>2.037587264092801</v>
+        <v>2.069860064531996</v>
       </c>
       <c r="U51">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V51">
         <v>0.34</v>
       </c>
       <c r="W51">
-        <v>0.03319799999999999</v>
+        <v>0.034188</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y51">
-        <v>13.01807091429558</v>
+        <v>12.38827775384723</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1194002807732057</v>
+        <v>0.118958882032689</v>
       </c>
       <c r="C52">
-        <v>187.9581886041018</v>
+        <v>185.9829777260544</v>
       </c>
       <c r="D52">
-        <v>281.8081886041018</v>
+        <v>283.2659777260544</v>
       </c>
       <c r="E52">
-        <v>-54.84999999999999</v>
+        <v>-51.417</v>
       </c>
       <c r="F52">
-        <v>171.65</v>
+        <v>175.083</v>
       </c>
       <c r="G52">
         <v>77.8</v>
@@ -5676,28 +5676,28 @@
         <v>110.15</v>
       </c>
       <c r="M52">
-        <v>8.89147</v>
+        <v>9.0692994</v>
       </c>
       <c r="N52">
-        <v>101.25853</v>
+        <v>101.0807006</v>
       </c>
       <c r="O52">
-        <v>34.4279002</v>
+        <v>34.367438204</v>
       </c>
       <c r="P52">
-        <v>66.8306298</v>
+        <v>66.713262396</v>
       </c>
       <c r="Q52">
-        <v>65.43062979999999</v>
+        <v>65.313262396</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2046125615464114</v>
+        <v>0.2071898000667122</v>
       </c>
       <c r="T52">
-        <v>2.069860064531996</v>
+        <v>2.103450122131974</v>
       </c>
       <c r="U52">
         <v>0.0518</v>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>12.38827775384723</v>
+        <v>12.14537034690905</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.118958882032689</v>
+        <v>0.1185174832921722</v>
       </c>
       <c r="C53">
-        <v>185.9829777260544</v>
+        <v>184.0229275121472</v>
       </c>
       <c r="D53">
-        <v>283.2659777260544</v>
+        <v>284.7389275121473</v>
       </c>
       <c r="E53">
-        <v>-51.417</v>
+        <v>-47.98399999999998</v>
       </c>
       <c r="F53">
-        <v>175.083</v>
+        <v>178.516</v>
       </c>
       <c r="G53">
         <v>77.8</v>
@@ -5758,28 +5758,28 @@
         <v>110.15</v>
       </c>
       <c r="M53">
-        <v>9.0692994</v>
+        <v>9.2471288</v>
       </c>
       <c r="N53">
-        <v>101.0807006</v>
+        <v>100.9028712</v>
       </c>
       <c r="O53">
-        <v>34.367438204</v>
+        <v>34.306976208</v>
       </c>
       <c r="P53">
-        <v>66.713262396</v>
+        <v>66.59589499200001</v>
       </c>
       <c r="Q53">
-        <v>65.313262396</v>
+        <v>65.19589499200001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2071898000667122</v>
+        <v>0.2098744235253588</v>
       </c>
       <c r="T53">
-        <v>2.103450122131974</v>
+        <v>2.138439765465284</v>
       </c>
       <c r="U53">
         <v>0.0518</v>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>12.14537034690905</v>
+        <v>11.91180553254541</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1185174832921722</v>
+        <v>0.1180760845516555</v>
       </c>
       <c r="C54">
-        <v>184.0229275121472</v>
+        <v>182.0782756996003</v>
       </c>
       <c r="D54">
-        <v>284.7389275121473</v>
+        <v>286.2272756996003</v>
       </c>
       <c r="E54">
-        <v>-47.98399999999998</v>
+        <v>-44.55099999999999</v>
       </c>
       <c r="F54">
-        <v>178.516</v>
+        <v>181.949</v>
       </c>
       <c r="G54">
         <v>77.8</v>
@@ -5840,28 +5840,28 @@
         <v>110.15</v>
       </c>
       <c r="M54">
-        <v>9.2471288</v>
+        <v>9.424958200000001</v>
       </c>
       <c r="N54">
-        <v>100.9028712</v>
+        <v>100.7250418</v>
       </c>
       <c r="O54">
-        <v>34.306976208</v>
+        <v>34.246514212</v>
       </c>
       <c r="P54">
-        <v>66.59589499200001</v>
+        <v>66.47852758799999</v>
       </c>
       <c r="Q54">
-        <v>65.19589499200001</v>
+        <v>65.07852758799999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2098744235253588</v>
+        <v>0.212673286280118</v>
       </c>
       <c r="T54">
-        <v>2.138439765465284</v>
+        <v>2.174918329791502</v>
       </c>
       <c r="U54">
         <v>0.0518</v>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>11.91180553254541</v>
+        <v>11.68705448476153</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1180760845516555</v>
+        <v>0.1176346858111387</v>
       </c>
       <c r="C55">
-        <v>182.0782756996003</v>
+        <v>180.1492650224211</v>
       </c>
       <c r="D55">
-        <v>286.2272756996003</v>
+        <v>287.7312650224211</v>
       </c>
       <c r="E55">
-        <v>-44.55099999999999</v>
+        <v>-41.11799999999999</v>
       </c>
       <c r="F55">
-        <v>181.949</v>
+        <v>185.382</v>
       </c>
       <c r="G55">
         <v>77.8</v>
@@ -5922,28 +5922,28 @@
         <v>110.15</v>
       </c>
       <c r="M55">
-        <v>9.424958200000001</v>
+        <v>9.602787599999999</v>
       </c>
       <c r="N55">
-        <v>100.7250418</v>
+        <v>100.5472124</v>
       </c>
       <c r="O55">
-        <v>34.246514212</v>
+        <v>34.18605221600001</v>
       </c>
       <c r="P55">
-        <v>66.47852758799999</v>
+        <v>66.361160184</v>
       </c>
       <c r="Q55">
-        <v>65.07852758799999</v>
+        <v>64.96116018399999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.212673286280118</v>
+        <v>0.2155938387198668</v>
       </c>
       <c r="T55">
-        <v>2.174918329791502</v>
+        <v>2.212982918653642</v>
       </c>
       <c r="U55">
         <v>0.0518</v>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>11.68705448476153</v>
+        <v>11.47062754985854</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1176346858111387</v>
+        <v>0.117193287070622</v>
       </c>
       <c r="C56">
-        <v>180.1492650224211</v>
+        <v>178.2361433433771</v>
       </c>
       <c r="D56">
-        <v>287.7312650224211</v>
+        <v>289.2511433433771</v>
       </c>
       <c r="E56">
-        <v>-41.11799999999999</v>
+        <v>-37.68499999999997</v>
       </c>
       <c r="F56">
-        <v>185.382</v>
+        <v>188.815</v>
       </c>
       <c r="G56">
         <v>77.8</v>
@@ -6004,28 +6004,28 @@
         <v>110.15</v>
       </c>
       <c r="M56">
-        <v>9.602787599999999</v>
+        <v>9.780617000000001</v>
       </c>
       <c r="N56">
-        <v>100.5472124</v>
+        <v>100.369383</v>
       </c>
       <c r="O56">
-        <v>34.18605221600001</v>
+        <v>34.12559022</v>
       </c>
       <c r="P56">
-        <v>66.361160184</v>
+        <v>66.24379278000001</v>
       </c>
       <c r="Q56">
-        <v>64.96116018399999</v>
+        <v>64.84379278</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2155938387198668</v>
+        <v>0.2186441934902711</v>
       </c>
       <c r="T56">
-        <v>2.212982918653642</v>
+        <v>2.252739267020766</v>
       </c>
       <c r="U56">
         <v>0.0518</v>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>11.47062754985854</v>
+        <v>11.26207068531566</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.117193287070622</v>
+        <v>0.1167518883301052</v>
       </c>
       <c r="C57">
-        <v>178.2361433433771</v>
+        <v>176.3391637901732</v>
       </c>
       <c r="D57">
-        <v>289.2511433433771</v>
+        <v>290.7871637901732</v>
       </c>
       <c r="E57">
-        <v>-37.68499999999997</v>
+        <v>-34.25199999999998</v>
       </c>
       <c r="F57">
-        <v>188.815</v>
+        <v>192.248</v>
       </c>
       <c r="G57">
         <v>77.8</v>
@@ -6086,28 +6086,28 @@
         <v>110.15</v>
       </c>
       <c r="M57">
-        <v>9.780617000000001</v>
+        <v>9.958446400000001</v>
       </c>
       <c r="N57">
-        <v>100.369383</v>
+        <v>100.1915536</v>
       </c>
       <c r="O57">
-        <v>34.12559022</v>
+        <v>34.06512822400001</v>
       </c>
       <c r="P57">
-        <v>66.24379278000001</v>
+        <v>66.126425376</v>
       </c>
       <c r="Q57">
-        <v>64.84379278</v>
+        <v>64.72642537599999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2186441934902711</v>
+        <v>0.2218332007502392</v>
       </c>
       <c r="T57">
-        <v>2.252739267020766</v>
+        <v>2.294302722131851</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>11.26207068531566</v>
+        <v>11.06096228022074</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1167518883301052</v>
+        <v>0.1163104895895885</v>
       </c>
       <c r="C58">
-        <v>176.3391637901732</v>
+        <v>174.4585848959909</v>
       </c>
       <c r="D58">
-        <v>290.7871637901732</v>
+        <v>292.3395848959909</v>
       </c>
       <c r="E58">
-        <v>-34.25199999999998</v>
+        <v>-30.81899999999996</v>
       </c>
       <c r="F58">
-        <v>192.248</v>
+        <v>195.681</v>
       </c>
       <c r="G58">
         <v>77.8</v>
@@ -6168,28 +6168,28 @@
         <v>110.15</v>
       </c>
       <c r="M58">
-        <v>9.958446400000001</v>
+        <v>10.1362758</v>
       </c>
       <c r="N58">
-        <v>100.1915536</v>
+        <v>100.0137242</v>
       </c>
       <c r="O58">
-        <v>34.06512822400001</v>
+        <v>34.004666228</v>
       </c>
       <c r="P58">
-        <v>66.126425376</v>
+        <v>66.00905797199999</v>
       </c>
       <c r="Q58">
-        <v>64.72642537599999</v>
+        <v>64.60905797199999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2218332007502392</v>
+        <v>0.2251705339292756</v>
       </c>
       <c r="T58">
-        <v>2.294302722131851</v>
+        <v>2.33779936120159</v>
       </c>
       <c r="U58">
         <v>0.0518</v>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>11.06096228022074</v>
+        <v>10.8669103103923</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1163104895895885</v>
+        <v>0.1158690908490717</v>
       </c>
       <c r="C59">
-        <v>174.4585848959909</v>
+        <v>172.594670744553</v>
       </c>
       <c r="D59">
-        <v>292.3395848959909</v>
+        <v>293.908670744553</v>
       </c>
       <c r="E59">
-        <v>-30.81899999999996</v>
+        <v>-27.38599999999997</v>
       </c>
       <c r="F59">
-        <v>195.681</v>
+        <v>199.114</v>
       </c>
       <c r="G59">
         <v>77.8</v>
@@ -6250,28 +6250,28 @@
         <v>110.15</v>
       </c>
       <c r="M59">
-        <v>10.1362758</v>
+        <v>10.3141052</v>
       </c>
       <c r="N59">
-        <v>100.0137242</v>
+        <v>99.83589480000001</v>
       </c>
       <c r="O59">
-        <v>34.004666228</v>
+        <v>33.944204232</v>
       </c>
       <c r="P59">
-        <v>66.00905797199999</v>
+        <v>65.891690568</v>
       </c>
       <c r="Q59">
-        <v>64.60905797199999</v>
+        <v>64.491690568</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2251705339292756</v>
+        <v>0.2286667877358851</v>
       </c>
       <c r="T59">
-        <v>2.33779936120159</v>
+        <v>2.38336726879846</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>10.8669103103923</v>
+        <v>10.67954978779933</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1158690908490717</v>
+        <v>0.115427692108555</v>
       </c>
       <c r="C60">
-        <v>172.594670744553</v>
+        <v>170.747691119886</v>
       </c>
       <c r="D60">
-        <v>293.908670744553</v>
+        <v>295.494691119886</v>
       </c>
       <c r="E60">
-        <v>-27.386</v>
+        <v>-23.953</v>
       </c>
       <c r="F60">
-        <v>199.114</v>
+        <v>202.547</v>
       </c>
       <c r="G60">
         <v>77.8</v>
@@ -6332,28 +6332,28 @@
         <v>110.15</v>
       </c>
       <c r="M60">
-        <v>10.3141052</v>
+        <v>10.4919346</v>
       </c>
       <c r="N60">
-        <v>99.83589480000001</v>
+        <v>99.6580654</v>
       </c>
       <c r="O60">
-        <v>33.944204232</v>
+        <v>33.883742236</v>
       </c>
       <c r="P60">
-        <v>65.891690568</v>
+        <v>65.77432316399999</v>
       </c>
       <c r="Q60">
-        <v>64.491690568</v>
+        <v>64.37432316399999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2286667877358851</v>
+        <v>0.2323335905086707</v>
       </c>
       <c r="T60">
-        <v>2.383367268798459</v>
+        <v>2.431158001156152</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>10.67954978779933</v>
+        <v>10.49854046936206</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.115427692108555</v>
+        <v>0.1149862933680383</v>
       </c>
       <c r="C61">
-        <v>170.747691119886</v>
+        <v>168.9179216609574</v>
       </c>
       <c r="D61">
-        <v>295.494691119886</v>
+        <v>297.0979216609574</v>
       </c>
       <c r="E61">
-        <v>-23.953</v>
+        <v>-20.52000000000001</v>
       </c>
       <c r="F61">
-        <v>202.547</v>
+        <v>205.98</v>
       </c>
       <c r="G61">
         <v>77.8</v>
@@ -6414,28 +6414,28 @@
         <v>110.15</v>
       </c>
       <c r="M61">
-        <v>10.4919346</v>
+        <v>10.669764</v>
       </c>
       <c r="N61">
-        <v>99.6580654</v>
+        <v>99.480236</v>
       </c>
       <c r="O61">
-        <v>33.883742236</v>
+        <v>33.82328024</v>
       </c>
       <c r="P61">
-        <v>65.77432316399999</v>
+        <v>65.65695576</v>
       </c>
       <c r="Q61">
-        <v>64.37432316399999</v>
+        <v>64.25695576</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2323335905086707</v>
+        <v>0.2361837334200956</v>
       </c>
       <c r="T61">
-        <v>2.431158001156152</v>
+        <v>2.481338270131729</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>10.49854046936206</v>
+        <v>10.32356479487269</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1149862933680383</v>
+        <v>0.1145448946275215</v>
       </c>
       <c r="C62">
-        <v>168.9179216609574</v>
+        <v>167.1056440213742</v>
       </c>
       <c r="D62">
-        <v>297.0979216609574</v>
+        <v>298.7186440213742</v>
       </c>
       <c r="E62">
-        <v>-20.52000000000001</v>
+        <v>-17.08699999999999</v>
       </c>
       <c r="F62">
-        <v>205.98</v>
+        <v>209.413</v>
       </c>
       <c r="G62">
         <v>77.8</v>
@@ -6496,28 +6496,28 @@
         <v>110.15</v>
       </c>
       <c r="M62">
-        <v>10.669764</v>
+        <v>10.8475934</v>
       </c>
       <c r="N62">
-        <v>99.480236</v>
+        <v>99.30240660000001</v>
       </c>
       <c r="O62">
-        <v>33.82328024</v>
+        <v>33.76281824400001</v>
       </c>
       <c r="P62">
-        <v>65.65695576</v>
+        <v>65.539588356</v>
       </c>
       <c r="Q62">
-        <v>64.25695576</v>
+        <v>64.13958835599999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2361837334200956</v>
+        <v>0.2402313195577475</v>
       </c>
       <c r="T62">
-        <v>2.481338270131729</v>
+        <v>2.53409188623426</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>10.32356479487269</v>
+        <v>10.15432602774363</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1145448946275215</v>
+        <v>0.1141034958870048</v>
       </c>
       <c r="C63">
-        <v>167.1056440213742</v>
+        <v>165.3111460343382</v>
       </c>
       <c r="D63">
-        <v>298.7186440213742</v>
+        <v>300.3571460343381</v>
       </c>
       <c r="E63">
-        <v>-17.08699999999999</v>
+        <v>-13.654</v>
       </c>
       <c r="F63">
-        <v>209.413</v>
+        <v>212.846</v>
       </c>
       <c r="G63">
         <v>77.8</v>
@@ -6578,28 +6578,28 @@
         <v>110.15</v>
       </c>
       <c r="M63">
-        <v>10.8475934</v>
+        <v>11.0254228</v>
       </c>
       <c r="N63">
-        <v>99.30240660000001</v>
+        <v>99.1245772</v>
       </c>
       <c r="O63">
-        <v>33.76281824400001</v>
+        <v>33.702356248</v>
       </c>
       <c r="P63">
-        <v>65.539588356</v>
+        <v>65.422220952</v>
       </c>
       <c r="Q63">
-        <v>64.13958835599999</v>
+        <v>64.022220952</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2402313195577475</v>
+        <v>0.2444919365447494</v>
       </c>
       <c r="T63">
-        <v>2.53409188623426</v>
+        <v>2.589622008447449</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>10.15432602774363</v>
+        <v>9.990546575683249</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1141034958870048</v>
+        <v>0.113662097146488</v>
       </c>
       <c r="C64">
-        <v>165.3111460343382</v>
+        <v>163.534721883058</v>
       </c>
       <c r="D64">
-        <v>300.3571460343381</v>
+        <v>302.013721883058</v>
       </c>
       <c r="E64">
-        <v>-13.654</v>
+        <v>-10.221</v>
       </c>
       <c r="F64">
-        <v>212.846</v>
+        <v>216.279</v>
       </c>
       <c r="G64">
         <v>77.8</v>
@@ -6660,28 +6660,28 @@
         <v>110.15</v>
       </c>
       <c r="M64">
-        <v>11.0254228</v>
+        <v>11.2032522</v>
       </c>
       <c r="N64">
-        <v>99.1245772</v>
+        <v>98.94674780000001</v>
       </c>
       <c r="O64">
-        <v>33.702356248</v>
+        <v>33.64189425200001</v>
       </c>
       <c r="P64">
-        <v>65.422220952</v>
+        <v>65.30485354800001</v>
       </c>
       <c r="Q64">
-        <v>64.022220952</v>
+        <v>63.90485354800001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2444919365447494</v>
+        <v>0.2489828571526703</v>
       </c>
       <c r="T64">
-        <v>2.589622008447449</v>
+        <v>2.648153758888379</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>9.990546575683249</v>
+        <v>9.831966471307323</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.113662097146488</v>
+        <v>0.1139387784059712</v>
       </c>
       <c r="C65">
-        <v>163.534721883058</v>
+        <v>159.0612032988888</v>
       </c>
       <c r="D65">
-        <v>302.013721883058</v>
+        <v>300.9732032988888</v>
       </c>
       <c r="E65">
-        <v>-10.221</v>
+        <v>-6.787999999999982</v>
       </c>
       <c r="F65">
-        <v>216.279</v>
+        <v>219.712</v>
       </c>
       <c r="G65">
         <v>77.8</v>
@@ -6742,45 +6742,45 @@
         <v>110.15</v>
       </c>
       <c r="M65">
-        <v>11.2032522</v>
+        <v>11.754592</v>
       </c>
       <c r="N65">
-        <v>98.94674780000001</v>
+        <v>98.395408</v>
       </c>
       <c r="O65">
-        <v>33.64189425200001</v>
+        <v>33.45443872000001</v>
       </c>
       <c r="P65">
-        <v>65.30485354800001</v>
+        <v>64.94096927999999</v>
       </c>
       <c r="Q65">
-        <v>63.90485354800001</v>
+        <v>63.54096927999998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2489828571526703</v>
+        <v>0.2537232733499202</v>
       </c>
       <c r="T65">
-        <v>2.648153758888379</v>
+        <v>2.709937273242693</v>
       </c>
       <c r="U65">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V65">
         <v>0.34</v>
       </c>
       <c r="W65">
-        <v>0.034188</v>
+        <v>0.03530999999999999</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>9.831966471307323</v>
+        <v>9.370805894411307</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1139387784059712</v>
+        <v>0.1135085996654545</v>
       </c>
       <c r="C66">
-        <v>159.0612032988888</v>
+        <v>157.2490905558688</v>
       </c>
       <c r="D66">
-        <v>300.9732032988888</v>
+        <v>302.5940905558688</v>
       </c>
       <c r="E66">
-        <v>-6.787999999999982</v>
+        <v>-3.35499999999999</v>
       </c>
       <c r="F66">
-        <v>219.712</v>
+        <v>223.145</v>
       </c>
       <c r="G66">
         <v>77.8</v>
@@ -6824,28 +6824,28 @@
         <v>110.15</v>
       </c>
       <c r="M66">
-        <v>11.754592</v>
+        <v>11.9382575</v>
       </c>
       <c r="N66">
-        <v>98.395408</v>
+        <v>98.2117425</v>
       </c>
       <c r="O66">
-        <v>33.45443872000001</v>
+        <v>33.39199245</v>
       </c>
       <c r="P66">
-        <v>64.94096927999999</v>
+        <v>64.81975005</v>
       </c>
       <c r="Q66">
-        <v>63.54096927999998</v>
+        <v>63.41975004999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2537232733499202</v>
+        <v>0.2587345704727272</v>
       </c>
       <c r="T66">
-        <v>2.709937273242693</v>
+        <v>2.77525127413154</v>
       </c>
       <c r="U66">
         <v>0.0535</v>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>9.370805894411307</v>
+        <v>9.226639649881902</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1135085996654545</v>
+        <v>0.1130784209249378</v>
       </c>
       <c r="C67">
-        <v>157.2490905558688</v>
+        <v>155.4545308789789</v>
       </c>
       <c r="D67">
-        <v>302.5940905558688</v>
+        <v>304.2325308789789</v>
       </c>
       <c r="E67">
-        <v>-3.35499999999999</v>
+        <v>0.07800000000003138</v>
       </c>
       <c r="F67">
-        <v>223.145</v>
+        <v>226.578</v>
       </c>
       <c r="G67">
         <v>77.8</v>
@@ -6906,28 +6906,28 @@
         <v>110.15</v>
       </c>
       <c r="M67">
-        <v>11.9382575</v>
+        <v>12.121923</v>
       </c>
       <c r="N67">
-        <v>98.2117425</v>
+        <v>98.02807700000001</v>
       </c>
       <c r="O67">
-        <v>33.39199245</v>
+        <v>33.32954618000001</v>
       </c>
       <c r="P67">
-        <v>64.81975005</v>
+        <v>64.69853082</v>
       </c>
       <c r="Q67">
-        <v>63.41975004999999</v>
+        <v>63.29853082</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2587345704727272</v>
+        <v>0.2640406497792288</v>
       </c>
       <c r="T67">
-        <v>2.77525127413154</v>
+        <v>2.844407275072672</v>
       </c>
       <c r="U67">
         <v>0.0535</v>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>9.226639649881902</v>
+        <v>9.086842079429147</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1130784209249378</v>
+        <v>0.112648242184421</v>
       </c>
       <c r="C68">
-        <v>155.4545308789789</v>
+        <v>153.6778109515027</v>
       </c>
       <c r="D68">
-        <v>304.2325308789789</v>
+        <v>305.8888109515028</v>
       </c>
       <c r="E68">
-        <v>0.07800000000003138</v>
+        <v>3.511000000000024</v>
       </c>
       <c r="F68">
-        <v>226.578</v>
+        <v>230.011</v>
       </c>
       <c r="G68">
         <v>77.8</v>
@@ -6988,28 +6988,28 @@
         <v>110.15</v>
       </c>
       <c r="M68">
-        <v>12.121923</v>
+        <v>12.3055885</v>
       </c>
       <c r="N68">
-        <v>98.02807700000001</v>
+        <v>97.84441150000001</v>
       </c>
       <c r="O68">
-        <v>33.32954618000001</v>
+        <v>33.26709991000001</v>
       </c>
       <c r="P68">
-        <v>64.69853082</v>
+        <v>64.57731158999999</v>
       </c>
       <c r="Q68">
-        <v>63.29853082</v>
+        <v>63.17731158999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2640406497792288</v>
+        <v>0.2696683096497607</v>
       </c>
       <c r="T68">
-        <v>2.844407275072672</v>
+        <v>2.917754548798114</v>
       </c>
       <c r="U68">
         <v>0.0535</v>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>9.086842079429147</v>
+        <v>8.951217570780951</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.112648242184421</v>
+        <v>0.1122180634439043</v>
       </c>
       <c r="C69">
-        <v>153.6778109515027</v>
+        <v>151.9192237338565</v>
       </c>
       <c r="D69">
-        <v>305.8888109515028</v>
+        <v>307.5632237338565</v>
       </c>
       <c r="E69">
-        <v>3.511000000000024</v>
+        <v>6.944000000000017</v>
       </c>
       <c r="F69">
-        <v>230.011</v>
+        <v>233.444</v>
       </c>
       <c r="G69">
         <v>77.8</v>
@@ -7070,28 +7070,28 @@
         <v>110.15</v>
       </c>
       <c r="M69">
-        <v>12.3055885</v>
+        <v>12.489254</v>
       </c>
       <c r="N69">
-        <v>97.84441150000001</v>
+        <v>97.660746</v>
       </c>
       <c r="O69">
-        <v>33.26709991000001</v>
+        <v>33.20465364</v>
       </c>
       <c r="P69">
-        <v>64.57731158999999</v>
+        <v>64.45609236</v>
       </c>
       <c r="Q69">
-        <v>63.17731158999999</v>
+        <v>63.05609235999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2696683096497607</v>
+        <v>0.2756476982622009</v>
       </c>
       <c r="T69">
-        <v>2.917754548798114</v>
+        <v>2.995686027131397</v>
       </c>
       <c r="U69">
         <v>0.0535</v>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>8.951217570780951</v>
+        <v>8.819582018269465</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1122180634439043</v>
+        <v>0.1117878847033875</v>
       </c>
       <c r="C70">
-        <v>151.9192237338565</v>
+        <v>150.1790686363372</v>
       </c>
       <c r="D70">
-        <v>307.5632237338565</v>
+        <v>309.2560686363372</v>
       </c>
       <c r="E70">
-        <v>6.944000000000017</v>
+        <v>10.37700000000004</v>
       </c>
       <c r="F70">
-        <v>233.444</v>
+        <v>236.877</v>
       </c>
       <c r="G70">
         <v>77.8</v>
@@ -7152,28 +7152,28 @@
         <v>110.15</v>
       </c>
       <c r="M70">
-        <v>12.489254</v>
+        <v>12.6729195</v>
       </c>
       <c r="N70">
-        <v>97.660746</v>
+        <v>97.4770805</v>
       </c>
       <c r="O70">
-        <v>33.20465364</v>
+        <v>33.14220737</v>
       </c>
       <c r="P70">
-        <v>64.45609236</v>
+        <v>64.33487313000001</v>
       </c>
       <c r="Q70">
-        <v>63.05609235999999</v>
+        <v>62.93487313</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2756476982622009</v>
+        <v>0.2820128538818953</v>
       </c>
       <c r="T70">
-        <v>2.995686027131397</v>
+        <v>3.078645342776505</v>
       </c>
       <c r="U70">
         <v>0.0535</v>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>8.819582018269465</v>
+        <v>8.691761989019183</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1117878847033875</v>
+        <v>0.1113577059628708</v>
       </c>
       <c r="C71">
-        <v>150.1790686363372</v>
+        <v>148.4576516976078</v>
       </c>
       <c r="D71">
-        <v>309.2560686363372</v>
+        <v>310.9676516976078</v>
       </c>
       <c r="E71">
-        <v>10.37700000000004</v>
+        <v>13.81000000000003</v>
       </c>
       <c r="F71">
-        <v>236.877</v>
+        <v>240.31</v>
       </c>
       <c r="G71">
         <v>77.8</v>
@@ -7234,28 +7234,28 @@
         <v>110.15</v>
       </c>
       <c r="M71">
-        <v>12.6729195</v>
+        <v>12.856585</v>
       </c>
       <c r="N71">
-        <v>97.4770805</v>
+        <v>97.29341500000001</v>
       </c>
       <c r="O71">
-        <v>33.14220737</v>
+        <v>33.07976110000001</v>
       </c>
       <c r="P71">
-        <v>64.33487313000001</v>
+        <v>64.2136539</v>
       </c>
       <c r="Q71">
-        <v>62.93487313</v>
+        <v>62.81365389999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2820128538818953</v>
+        <v>0.2888023532095693</v>
       </c>
       <c r="T71">
-        <v>3.078645342776505</v>
+        <v>3.16713527946462</v>
       </c>
       <c r="U71">
         <v>0.0535</v>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>8.691761989019183</v>
+        <v>8.567593960604626</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1113577059628708</v>
+        <v>0.110927527222354</v>
       </c>
       <c r="C72">
-        <v>148.4576516976078</v>
+        <v>146.7552857691423</v>
       </c>
       <c r="D72">
-        <v>310.9676516976078</v>
+        <v>312.6982857691423</v>
       </c>
       <c r="E72">
-        <v>13.81000000000003</v>
+        <v>17.24300000000002</v>
       </c>
       <c r="F72">
-        <v>240.31</v>
+        <v>243.743</v>
       </c>
       <c r="G72">
         <v>77.8</v>
@@ -7316,28 +7316,28 @@
         <v>110.15</v>
       </c>
       <c r="M72">
-        <v>12.856585</v>
+        <v>13.0402505</v>
       </c>
       <c r="N72">
-        <v>97.29341500000001</v>
+        <v>97.10974950000001</v>
       </c>
       <c r="O72">
-        <v>33.07976110000001</v>
+        <v>33.01731483</v>
       </c>
       <c r="P72">
-        <v>64.2136539</v>
+        <v>64.09243467</v>
       </c>
       <c r="Q72">
-        <v>62.81365389999999</v>
+        <v>62.69243467</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2888023532095693</v>
+        <v>0.2960600938701864</v>
       </c>
       <c r="T72">
-        <v>3.16713527946462</v>
+        <v>3.261727970407088</v>
       </c>
       <c r="U72">
         <v>0.0535</v>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>8.567593960604626</v>
+        <v>8.446923623131319</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.110927527222354</v>
+        <v>0.1104973484818373</v>
       </c>
       <c r="C73">
-        <v>146.7552857691423</v>
+        <v>145.0722907058633</v>
       </c>
       <c r="D73">
-        <v>312.6982857691423</v>
+        <v>314.4482907058633</v>
       </c>
       <c r="E73">
-        <v>17.24299999999999</v>
+        <v>20.67599999999999</v>
       </c>
       <c r="F73">
-        <v>243.743</v>
+        <v>247.176</v>
       </c>
       <c r="G73">
         <v>77.8</v>
@@ -7398,28 +7398,28 @@
         <v>110.15</v>
       </c>
       <c r="M73">
-        <v>13.0402505</v>
+        <v>13.223916</v>
       </c>
       <c r="N73">
-        <v>97.10974950000001</v>
+        <v>96.926084</v>
       </c>
       <c r="O73">
-        <v>33.01731483</v>
+        <v>32.95486856</v>
       </c>
       <c r="P73">
-        <v>64.09243467</v>
+        <v>63.97121544</v>
       </c>
       <c r="Q73">
-        <v>62.69243467</v>
+        <v>62.57121544</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2960600938701863</v>
+        <v>0.3038362445779904</v>
       </c>
       <c r="T73">
-        <v>3.261727970407087</v>
+        <v>3.363077282131159</v>
       </c>
       <c r="U73">
         <v>0.0535</v>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>8.446923623131321</v>
+        <v>8.329605239476718</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1104973484818373</v>
+        <v>0.1100671697413206</v>
       </c>
       <c r="C74">
-        <v>145.0722907058633</v>
+        <v>143.4089935632183</v>
       </c>
       <c r="D74">
-        <v>314.4482907058633</v>
+        <v>316.2179935632183</v>
       </c>
       <c r="E74">
-        <v>20.67599999999999</v>
+        <v>24.10900000000001</v>
       </c>
       <c r="F74">
-        <v>247.176</v>
+        <v>250.609</v>
       </c>
       <c r="G74">
         <v>77.8</v>
@@ -7480,28 +7480,28 @@
         <v>110.15</v>
       </c>
       <c r="M74">
-        <v>13.223916</v>
+        <v>13.4075815</v>
       </c>
       <c r="N74">
-        <v>96.926084</v>
+        <v>96.7424185</v>
       </c>
       <c r="O74">
-        <v>32.95486856</v>
+        <v>32.89242229</v>
       </c>
       <c r="P74">
-        <v>63.97121544</v>
+        <v>63.84999621</v>
       </c>
       <c r="Q74">
-        <v>62.57121544</v>
+        <v>62.44999620999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3038362445779904</v>
+        <v>0.3121884064493354</v>
       </c>
       <c r="T74">
-        <v>3.363077282131159</v>
+        <v>3.471933950279237</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>8.329605239476718</v>
+        <v>8.215501058114022</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1100671697413206</v>
+        <v>0.1096369910008038</v>
       </c>
       <c r="C75">
-        <v>143.4089935632183</v>
+        <v>141.7657288009475</v>
       </c>
       <c r="D75">
-        <v>316.2179935632183</v>
+        <v>318.0077288009475</v>
       </c>
       <c r="E75">
-        <v>24.10900000000001</v>
+        <v>27.542</v>
       </c>
       <c r="F75">
-        <v>250.609</v>
+        <v>254.042</v>
       </c>
       <c r="G75">
         <v>77.8</v>
@@ -7562,28 +7562,28 @@
         <v>110.15</v>
       </c>
       <c r="M75">
-        <v>13.4075815</v>
+        <v>13.591247</v>
       </c>
       <c r="N75">
-        <v>96.7424185</v>
+        <v>96.55875300000001</v>
       </c>
       <c r="O75">
-        <v>32.89242229</v>
+        <v>32.82997602</v>
       </c>
       <c r="P75">
-        <v>63.84999621</v>
+        <v>63.72877698000001</v>
       </c>
       <c r="Q75">
-        <v>62.44999620999999</v>
+        <v>62.32877698</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3121884064493354</v>
+        <v>0.3211830423107839</v>
       </c>
       <c r="T75">
-        <v>3.471933950279237</v>
+        <v>3.589164208284859</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>8.215501058114022</v>
+        <v>8.104480773544916</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1096369910008038</v>
+        <v>0.109206812260287</v>
       </c>
       <c r="C76">
-        <v>141.7657288009475</v>
+        <v>140.1428384938114</v>
       </c>
       <c r="D76">
-        <v>318.0077288009475</v>
+        <v>319.8178384938115</v>
       </c>
       <c r="E76">
-        <v>27.542</v>
+        <v>30.97500000000002</v>
       </c>
       <c r="F76">
-        <v>254.042</v>
+        <v>257.475</v>
       </c>
       <c r="G76">
         <v>77.8</v>
@@ -7644,28 +7644,28 @@
         <v>110.15</v>
       </c>
       <c r="M76">
-        <v>13.591247</v>
+        <v>13.7749125</v>
       </c>
       <c r="N76">
-        <v>96.55875300000001</v>
+        <v>96.37508750000001</v>
       </c>
       <c r="O76">
-        <v>32.82997602</v>
+        <v>32.76752975</v>
       </c>
       <c r="P76">
-        <v>63.72877698000001</v>
+        <v>63.60755775000001</v>
       </c>
       <c r="Q76">
-        <v>62.32877698</v>
+        <v>62.20755775</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3211830423107839</v>
+        <v>0.3308972490411482</v>
       </c>
       <c r="T76">
-        <v>3.589164208284859</v>
+        <v>3.715772886930931</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>8.104480773544916</v>
+        <v>7.996421029897649</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.109206812260287</v>
+        <v>0.1087766335197703</v>
       </c>
       <c r="C77">
-        <v>140.1428384938114</v>
+        <v>138.5406725495559</v>
       </c>
       <c r="D77">
-        <v>319.8178384938115</v>
+        <v>321.6486725495559</v>
       </c>
       <c r="E77">
-        <v>30.97500000000002</v>
+        <v>34.40800000000002</v>
       </c>
       <c r="F77">
-        <v>257.475</v>
+        <v>260.908</v>
       </c>
       <c r="G77">
         <v>77.8</v>
@@ -7726,28 +7726,28 @@
         <v>110.15</v>
       </c>
       <c r="M77">
-        <v>13.7749125</v>
+        <v>13.958578</v>
       </c>
       <c r="N77">
-        <v>96.37508750000001</v>
+        <v>96.191422</v>
       </c>
       <c r="O77">
-        <v>32.76752975</v>
+        <v>32.70508348000001</v>
       </c>
       <c r="P77">
-        <v>63.60755775000001</v>
+        <v>63.48633852</v>
       </c>
       <c r="Q77">
-        <v>62.20755775</v>
+        <v>62.08633851999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3308972490411482</v>
+        <v>0.341420972999043</v>
       </c>
       <c r="T77">
-        <v>3.715772886930931</v>
+        <v>3.85293228879751</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>7.996421029897649</v>
+        <v>7.891204963714785</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1087766335197703</v>
+        <v>0.1083464547792536</v>
       </c>
       <c r="C78">
-        <v>138.5406725495559</v>
+        <v>136.9595889344076</v>
       </c>
       <c r="D78">
-        <v>321.6486725495559</v>
+        <v>323.5005889344076</v>
       </c>
       <c r="E78">
-        <v>34.40800000000002</v>
+        <v>37.84100000000001</v>
       </c>
       <c r="F78">
-        <v>260.908</v>
+        <v>264.341</v>
       </c>
       <c r="G78">
         <v>77.8</v>
@@ -7808,28 +7808,28 @@
         <v>110.15</v>
       </c>
       <c r="M78">
-        <v>13.958578</v>
+        <v>14.1422435</v>
       </c>
       <c r="N78">
-        <v>96.191422</v>
+        <v>96.0077565</v>
       </c>
       <c r="O78">
-        <v>32.70508348000001</v>
+        <v>32.64263721</v>
       </c>
       <c r="P78">
-        <v>63.48633852</v>
+        <v>63.36511929</v>
       </c>
       <c r="Q78">
-        <v>62.08633851999999</v>
+        <v>61.96511928999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.341420972999043</v>
+        <v>0.352859803388059</v>
       </c>
       <c r="T78">
-        <v>3.85293228879751</v>
+        <v>4.002018595174225</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>7.891204963714785</v>
+        <v>7.788721782367841</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1083464547792536</v>
+        <v>0.1079162760387368</v>
       </c>
       <c r="C79">
-        <v>136.9595889344076</v>
+        <v>135.3999539064033</v>
       </c>
       <c r="D79">
-        <v>323.5005889344076</v>
+        <v>325.3739539064033</v>
       </c>
       <c r="E79">
-        <v>37.84100000000001</v>
+        <v>41.274</v>
       </c>
       <c r="F79">
-        <v>264.341</v>
+        <v>267.774</v>
       </c>
       <c r="G79">
         <v>77.8</v>
@@ -7890,28 +7890,28 @@
         <v>110.15</v>
       </c>
       <c r="M79">
-        <v>14.1422435</v>
+        <v>14.325909</v>
       </c>
       <c r="N79">
-        <v>96.0077565</v>
+        <v>95.82409100000001</v>
       </c>
       <c r="O79">
-        <v>32.64263721</v>
+        <v>32.58019094000001</v>
       </c>
       <c r="P79">
-        <v>63.36511929</v>
+        <v>63.24390006</v>
       </c>
       <c r="Q79">
-        <v>61.96511928999999</v>
+        <v>61.84390006</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.352859803388059</v>
+        <v>0.3653385274488037</v>
       </c>
       <c r="T79">
-        <v>4.002018595174225</v>
+        <v>4.164658202130641</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>7.788721782367841</v>
+        <v>7.688866374901587</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1079162760387368</v>
+        <v>0.1079032172982201</v>
       </c>
       <c r="C80">
-        <v>135.3999539064033</v>
+        <v>132.0241621752147</v>
       </c>
       <c r="D80">
-        <v>325.3739539064033</v>
+        <v>325.4311621752146</v>
       </c>
       <c r="E80">
-        <v>41.274</v>
+        <v>44.70699999999999</v>
       </c>
       <c r="F80">
-        <v>267.774</v>
+        <v>271.207</v>
       </c>
       <c r="G80">
         <v>77.8</v>
@@ -7972,45 +7972,45 @@
         <v>110.15</v>
       </c>
       <c r="M80">
-        <v>14.325909</v>
+        <v>14.7265401</v>
       </c>
       <c r="N80">
-        <v>95.82409100000001</v>
+        <v>95.42345990000001</v>
       </c>
       <c r="O80">
-        <v>32.58019094000001</v>
+        <v>32.44397636600001</v>
       </c>
       <c r="P80">
-        <v>63.24390006</v>
+        <v>62.979483534</v>
       </c>
       <c r="Q80">
-        <v>61.84390006</v>
+        <v>61.579483534</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3653385274488037</v>
+        <v>0.3790057014200956</v>
       </c>
       <c r="T80">
-        <v>4.164658202130641</v>
+        <v>4.34278729546386</v>
       </c>
       <c r="U80">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V80">
         <v>0.34</v>
       </c>
       <c r="W80">
-        <v>0.03530999999999999</v>
+        <v>0.03583799999999999</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y80">
-        <v>7.688866374901587</v>
+        <v>7.479693074682221</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1079032172982201</v>
+        <v>0.1074783185577033</v>
       </c>
       <c r="C81">
-        <v>132.0241621752147</v>
+        <v>130.4636153884285</v>
       </c>
       <c r="D81">
-        <v>325.4311621752146</v>
+        <v>327.3036153884286</v>
       </c>
       <c r="E81">
-        <v>44.70699999999999</v>
+        <v>48.14000000000004</v>
       </c>
       <c r="F81">
-        <v>271.207</v>
+        <v>274.64</v>
       </c>
       <c r="G81">
         <v>77.8</v>
@@ -8054,28 +8054,28 @@
         <v>110.15</v>
       </c>
       <c r="M81">
-        <v>14.7265401</v>
+        <v>14.912952</v>
       </c>
       <c r="N81">
-        <v>95.42345990000001</v>
+        <v>95.237048</v>
       </c>
       <c r="O81">
-        <v>32.44397636600001</v>
+        <v>32.38059632</v>
       </c>
       <c r="P81">
-        <v>62.979483534</v>
+        <v>62.85645168</v>
       </c>
       <c r="Q81">
-        <v>61.579483534</v>
+        <v>61.45645167999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3790057014200956</v>
+        <v>0.3940395927885167</v>
       </c>
       <c r="T81">
-        <v>4.34278729546386</v>
+        <v>4.5387292981304</v>
       </c>
       <c r="U81">
         <v>0.0543</v>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>7.479693074682221</v>
+        <v>7.386196911248691</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1074783185577033</v>
+        <v>0.1070534198171866</v>
       </c>
       <c r="C82">
-        <v>130.4636153884285</v>
+        <v>128.9247405946289</v>
       </c>
       <c r="D82">
-        <v>327.3036153884286</v>
+        <v>329.1977405946289</v>
       </c>
       <c r="E82">
-        <v>48.14000000000004</v>
+        <v>51.57300000000004</v>
       </c>
       <c r="F82">
-        <v>274.64</v>
+        <v>278.073</v>
       </c>
       <c r="G82">
         <v>77.8</v>
@@ -8136,28 +8136,28 @@
         <v>110.15</v>
       </c>
       <c r="M82">
-        <v>14.912952</v>
+        <v>15.0993639</v>
       </c>
       <c r="N82">
-        <v>95.237048</v>
+        <v>95.05063610000001</v>
       </c>
       <c r="O82">
-        <v>32.38059632</v>
+        <v>32.317216274</v>
       </c>
       <c r="P82">
-        <v>62.85645168</v>
+        <v>62.733419826</v>
       </c>
       <c r="Q82">
-        <v>61.45645167999999</v>
+        <v>61.333419826</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3940395927885167</v>
+        <v>0.4106559990378242</v>
       </c>
       <c r="T82">
-        <v>4.5387292981304</v>
+        <v>4.75529677476184</v>
       </c>
       <c r="U82">
         <v>0.0543</v>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>7.386196911248691</v>
+        <v>7.295009295060436</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1070534198171866</v>
+        <v>0.1066285210766698</v>
       </c>
       <c r="C83">
-        <v>128.9247405946289</v>
+        <v>127.4079162351591</v>
       </c>
       <c r="D83">
-        <v>329.1977405946289</v>
+        <v>331.1139162351591</v>
       </c>
       <c r="E83">
-        <v>51.57300000000004</v>
+        <v>55.00600000000003</v>
       </c>
       <c r="F83">
-        <v>278.073</v>
+        <v>281.506</v>
       </c>
       <c r="G83">
         <v>77.8</v>
@@ -8218,28 +8218,28 @@
         <v>110.15</v>
       </c>
       <c r="M83">
-        <v>15.0993639</v>
+        <v>15.2857758</v>
       </c>
       <c r="N83">
-        <v>95.05063610000001</v>
+        <v>94.86422420000001</v>
       </c>
       <c r="O83">
-        <v>32.317216274</v>
+        <v>32.253836228</v>
       </c>
       <c r="P83">
-        <v>62.733419826</v>
+        <v>62.61038797200001</v>
       </c>
       <c r="Q83">
-        <v>61.333419826</v>
+        <v>61.210387972</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4106559990378242</v>
+        <v>0.4291186726481659</v>
       </c>
       <c r="T83">
-        <v>4.75529677476184</v>
+        <v>4.995927304352328</v>
       </c>
       <c r="U83">
         <v>0.0543</v>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>7.295009295060436</v>
+        <v>7.206045767071894</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1066285210766698</v>
+        <v>0.1062036223361531</v>
       </c>
       <c r="C84">
-        <v>127.4079162351591</v>
+        <v>125.9135296141904</v>
       </c>
       <c r="D84">
-        <v>331.1139162351591</v>
+        <v>333.0525296141904</v>
       </c>
       <c r="E84">
-        <v>55.00600000000003</v>
+        <v>58.43900000000002</v>
       </c>
       <c r="F84">
-        <v>281.506</v>
+        <v>284.939</v>
       </c>
       <c r="G84">
         <v>77.8</v>
@@ -8300,28 +8300,28 @@
         <v>110.15</v>
       </c>
       <c r="M84">
-        <v>15.2857758</v>
+        <v>15.4721877</v>
       </c>
       <c r="N84">
-        <v>94.86422420000001</v>
+        <v>94.6778123</v>
       </c>
       <c r="O84">
-        <v>32.253836228</v>
+        <v>32.19045618200001</v>
       </c>
       <c r="P84">
-        <v>62.61038797200001</v>
+        <v>62.48735611799999</v>
       </c>
       <c r="Q84">
-        <v>61.210387972</v>
+        <v>61.08735611799999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4291186726481659</v>
+        <v>0.449753425506783</v>
       </c>
       <c r="T84">
-        <v>4.995927304352328</v>
+        <v>5.264867308012286</v>
       </c>
       <c r="U84">
         <v>0.0543</v>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>7.206045767071894</v>
+        <v>7.119225938552955</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1062036223361531</v>
+        <v>0.1057787235956363</v>
       </c>
       <c r="C85">
-        <v>125.9135296141904</v>
+        <v>124.4419771597024</v>
       </c>
       <c r="D85">
-        <v>333.0525296141904</v>
+        <v>335.0139771597024</v>
       </c>
       <c r="E85">
-        <v>58.43900000000002</v>
+        <v>61.87200000000001</v>
       </c>
       <c r="F85">
-        <v>284.939</v>
+        <v>288.372</v>
       </c>
       <c r="G85">
         <v>77.8</v>
@@ -8382,28 +8382,28 @@
         <v>110.15</v>
       </c>
       <c r="M85">
-        <v>15.4721877</v>
+        <v>15.6585996</v>
       </c>
       <c r="N85">
-        <v>94.6778123</v>
+        <v>94.4914004</v>
       </c>
       <c r="O85">
-        <v>32.19045618200001</v>
+        <v>32.12707613600001</v>
       </c>
       <c r="P85">
-        <v>62.48735611799999</v>
+        <v>62.364324264</v>
       </c>
       <c r="Q85">
-        <v>61.08735611799999</v>
+        <v>60.96432426399999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.449753425506783</v>
+        <v>0.4729675224727273</v>
       </c>
       <c r="T85">
-        <v>5.264867308012286</v>
+        <v>5.567424812129738</v>
       </c>
       <c r="U85">
         <v>0.0543</v>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>7.119225938552955</v>
+        <v>7.034473248808278</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1057787235956363</v>
+        <v>0.1053538248551196</v>
       </c>
       <c r="C86">
-        <v>124.4419771597024</v>
+        <v>122.9936646937381</v>
       </c>
       <c r="D86">
-        <v>335.0139771597024</v>
+        <v>336.9986646937381</v>
       </c>
       <c r="E86">
-        <v>61.87200000000001</v>
+        <v>65.30500000000001</v>
       </c>
       <c r="F86">
-        <v>288.372</v>
+        <v>291.805</v>
       </c>
       <c r="G86">
         <v>77.8</v>
@@ -8464,28 +8464,28 @@
         <v>110.15</v>
       </c>
       <c r="M86">
-        <v>15.6585996</v>
+        <v>15.8450115</v>
       </c>
       <c r="N86">
-        <v>94.4914004</v>
+        <v>94.30498850000001</v>
       </c>
       <c r="O86">
-        <v>32.12707613600001</v>
+        <v>32.06369609000001</v>
       </c>
       <c r="P86">
-        <v>62.364324264</v>
+        <v>62.24129241</v>
       </c>
       <c r="Q86">
-        <v>60.96432426399999</v>
+        <v>60.84129240999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4729675224727271</v>
+        <v>0.499276832367464</v>
       </c>
       <c r="T86">
-        <v>5.567424812129734</v>
+        <v>5.91032331679618</v>
       </c>
       <c r="U86">
         <v>0.0543</v>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>7.034473248808278</v>
+        <v>6.951714739998769</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1053538248551196</v>
+        <v>0.1049289261146028</v>
       </c>
       <c r="C87">
-        <v>122.9936646937381</v>
+        <v>121.5690077123242</v>
       </c>
       <c r="D87">
-        <v>336.9986646937381</v>
+        <v>339.0070077123242</v>
       </c>
       <c r="E87">
-        <v>65.30500000000001</v>
+        <v>68.738</v>
       </c>
       <c r="F87">
-        <v>291.805</v>
+        <v>295.238</v>
       </c>
       <c r="G87">
         <v>77.8</v>
@@ -8546,28 +8546,28 @@
         <v>110.15</v>
       </c>
       <c r="M87">
-        <v>15.8450115</v>
+        <v>16.0314234</v>
       </c>
       <c r="N87">
-        <v>94.30498850000001</v>
+        <v>94.11857660000001</v>
       </c>
       <c r="O87">
-        <v>32.06369609000001</v>
+        <v>32.00031604400001</v>
       </c>
       <c r="P87">
-        <v>62.24129241</v>
+        <v>62.118260556</v>
       </c>
       <c r="Q87">
-        <v>60.84129240999999</v>
+        <v>60.718260556</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.499276832367464</v>
+        <v>0.529344615104306</v>
       </c>
       <c r="T87">
-        <v>5.91032331679618</v>
+        <v>6.302207322129259</v>
       </c>
       <c r="U87">
         <v>0.0543</v>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>6.951714739998769</v>
+        <v>6.870880847673202</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1049289261146028</v>
+        <v>0.1045040273740861</v>
       </c>
       <c r="C88">
-        <v>121.5690077123242</v>
+        <v>120.1684316754589</v>
       </c>
       <c r="D88">
-        <v>339.0070077123242</v>
+        <v>341.0394316754588</v>
       </c>
       <c r="E88">
-        <v>68.738</v>
+        <v>72.17099999999999</v>
       </c>
       <c r="F88">
-        <v>295.238</v>
+        <v>298.671</v>
       </c>
       <c r="G88">
         <v>77.8</v>
@@ -8628,28 +8628,28 @@
         <v>110.15</v>
       </c>
       <c r="M88">
-        <v>16.0314234</v>
+        <v>16.2178353</v>
       </c>
       <c r="N88">
-        <v>94.11857660000001</v>
+        <v>93.9321647</v>
       </c>
       <c r="O88">
-        <v>32.00031604400001</v>
+        <v>31.936935998</v>
       </c>
       <c r="P88">
-        <v>62.118260556</v>
+        <v>61.995228702</v>
       </c>
       <c r="Q88">
-        <v>60.718260556</v>
+        <v>60.59522870199999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.529344615104306</v>
+        <v>0.564038210569893</v>
       </c>
       <c r="T88">
-        <v>6.302207322129259</v>
+        <v>6.754381174436659</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>6.870880847673202</v>
+        <v>6.791905205745923</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1045040273740861</v>
+        <v>0.1040791286335693</v>
       </c>
       <c r="C89">
-        <v>120.1684316754589</v>
+        <v>118.7923723075956</v>
       </c>
       <c r="D89">
-        <v>341.0394316754588</v>
+        <v>343.0963723075956</v>
       </c>
       <c r="E89">
-        <v>72.17099999999999</v>
+        <v>75.60399999999998</v>
       </c>
       <c r="F89">
-        <v>298.671</v>
+        <v>302.104</v>
       </c>
       <c r="G89">
         <v>77.8</v>
@@ -8710,28 +8710,28 @@
         <v>110.15</v>
       </c>
       <c r="M89">
-        <v>16.2178353</v>
+        <v>16.4042472</v>
       </c>
       <c r="N89">
-        <v>93.9321647</v>
+        <v>93.74575280000001</v>
       </c>
       <c r="O89">
-        <v>31.936935998</v>
+        <v>31.873555952</v>
       </c>
       <c r="P89">
-        <v>61.995228702</v>
+        <v>61.872196848</v>
       </c>
       <c r="Q89">
-        <v>60.59522870199999</v>
+        <v>60.472196848</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.564038210569893</v>
+        <v>0.6045140719464113</v>
       </c>
       <c r="T89">
-        <v>6.754381174436659</v>
+        <v>7.28191733546196</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>6.791905205745923</v>
+        <v>6.714724464771538</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1040791286335693</v>
+        <v>0.1036542298930526</v>
       </c>
       <c r="C90">
-        <v>118.7923723075956</v>
+        <v>117.4412759090648</v>
       </c>
       <c r="D90">
-        <v>343.0963723075956</v>
+        <v>345.1782759090648</v>
       </c>
       <c r="E90">
-        <v>75.60399999999998</v>
+        <v>79.03700000000003</v>
       </c>
       <c r="F90">
-        <v>302.104</v>
+        <v>305.537</v>
       </c>
       <c r="G90">
         <v>77.8</v>
@@ -8792,28 +8792,28 @@
         <v>110.15</v>
       </c>
       <c r="M90">
-        <v>16.4042472</v>
+        <v>16.5906591</v>
       </c>
       <c r="N90">
-        <v>93.74575280000001</v>
+        <v>93.5593409</v>
       </c>
       <c r="O90">
-        <v>31.873555952</v>
+        <v>31.810175906</v>
       </c>
       <c r="P90">
-        <v>61.872196848</v>
+        <v>61.749164994</v>
       </c>
       <c r="Q90">
-        <v>60.472196848</v>
+        <v>60.34916499399999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6045140719464113</v>
+        <v>0.6523491808459327</v>
       </c>
       <c r="T90">
-        <v>7.28191733546196</v>
+        <v>7.905369162128224</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>6.714724464771538</v>
+        <v>6.639278122470733</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1036542298930526</v>
+        <v>0.1032293311525359</v>
       </c>
       <c r="C91">
-        <v>117.4412759090648</v>
+        <v>116.1155996789057</v>
       </c>
       <c r="D91">
-        <v>345.1782759090648</v>
+        <v>347.2855996789057</v>
       </c>
       <c r="E91">
-        <v>79.03700000000003</v>
+        <v>82.47000000000003</v>
       </c>
       <c r="F91">
-        <v>305.537</v>
+        <v>308.97</v>
       </c>
       <c r="G91">
         <v>77.8</v>
@@ -8874,28 +8874,28 @@
         <v>110.15</v>
       </c>
       <c r="M91">
-        <v>16.5906591</v>
+        <v>16.777071</v>
       </c>
       <c r="N91">
-        <v>93.5593409</v>
+        <v>93.372929</v>
       </c>
       <c r="O91">
-        <v>31.810175906</v>
+        <v>31.74679586</v>
       </c>
       <c r="P91">
-        <v>61.749164994</v>
+        <v>61.62613313999999</v>
       </c>
       <c r="Q91">
-        <v>60.34916499399999</v>
+        <v>60.22613313999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6523491808459327</v>
+        <v>0.7097513115253588</v>
       </c>
       <c r="T91">
-        <v>7.905369162128224</v>
+        <v>8.653511354127742</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>6.639278122470733</v>
+        <v>6.565508365554392</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1032293311525359</v>
+        <v>0.1028044324120191</v>
       </c>
       <c r="C92">
-        <v>116.1155996789057</v>
+        <v>114.8158120495928</v>
       </c>
       <c r="D92">
-        <v>347.2855996789057</v>
+        <v>349.4188120495928</v>
       </c>
       <c r="E92">
-        <v>82.47000000000003</v>
+        <v>85.90300000000002</v>
       </c>
       <c r="F92">
-        <v>308.97</v>
+        <v>312.403</v>
       </c>
       <c r="G92">
         <v>77.8</v>
@@ -8956,28 +8956,28 @@
         <v>110.15</v>
       </c>
       <c r="M92">
-        <v>16.777071</v>
+        <v>16.9634829</v>
       </c>
       <c r="N92">
-        <v>93.372929</v>
+        <v>93.1865171</v>
       </c>
       <c r="O92">
-        <v>31.74679586</v>
+        <v>31.683415814</v>
       </c>
       <c r="P92">
-        <v>61.62613313999999</v>
+        <v>61.503101286</v>
       </c>
       <c r="Q92">
-        <v>60.22613313999999</v>
+        <v>60.103101286</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7097513115253588</v>
+        <v>0.779909471244657</v>
       </c>
       <c r="T92">
-        <v>8.653511354127742</v>
+        <v>9.567907366571596</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>6.565508365554392</v>
+        <v>6.493359921976872</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1028044324120191</v>
+        <v>0.1023795336715023</v>
       </c>
       <c r="C93">
-        <v>114.8158120495928</v>
+        <v>113.5423930341781</v>
       </c>
       <c r="D93">
-        <v>349.4188120495928</v>
+        <v>351.5783930341781</v>
       </c>
       <c r="E93">
-        <v>85.90300000000002</v>
+        <v>89.33600000000001</v>
       </c>
       <c r="F93">
-        <v>312.403</v>
+        <v>315.836</v>
       </c>
       <c r="G93">
         <v>77.8</v>
@@ -9038,28 +9038,28 @@
         <v>110.15</v>
       </c>
       <c r="M93">
-        <v>16.9634829</v>
+        <v>17.1498948</v>
       </c>
       <c r="N93">
-        <v>93.1865171</v>
+        <v>93.00010520000001</v>
       </c>
       <c r="O93">
-        <v>31.683415814</v>
+        <v>31.620035768</v>
       </c>
       <c r="P93">
-        <v>61.503101286</v>
+        <v>61.380069432</v>
       </c>
       <c r="Q93">
-        <v>60.103101286</v>
+        <v>59.98006943199999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.779909471244657</v>
+        <v>0.8676071708937799</v>
       </c>
       <c r="T93">
-        <v>9.567907366571596</v>
+        <v>10.71090238212641</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>6.493359921976872</v>
+        <v>6.422779922824949</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1023795336715023</v>
+        <v>0.1019546349309856</v>
       </c>
       <c r="C94">
-        <v>113.5423930341781</v>
+        <v>112.2958345863838</v>
       </c>
       <c r="D94">
-        <v>351.5783930341781</v>
+        <v>353.7648345863838</v>
       </c>
       <c r="E94">
-        <v>89.33600000000001</v>
+        <v>92.76900000000001</v>
       </c>
       <c r="F94">
-        <v>315.836</v>
+        <v>319.269</v>
       </c>
       <c r="G94">
         <v>77.8</v>
@@ -9120,28 +9120,28 @@
         <v>110.15</v>
       </c>
       <c r="M94">
-        <v>17.1498948</v>
+        <v>17.3363067</v>
       </c>
       <c r="N94">
-        <v>93.00010520000001</v>
+        <v>92.81369330000001</v>
       </c>
       <c r="O94">
-        <v>31.620035768</v>
+        <v>31.55665572200001</v>
       </c>
       <c r="P94">
-        <v>61.380069432</v>
+        <v>61.25703757800001</v>
       </c>
       <c r="Q94">
-        <v>59.98006943199999</v>
+        <v>59.857037578</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.8676071708937799</v>
+        <v>0.9803613561569381</v>
       </c>
       <c r="T94">
-        <v>10.71090238212641</v>
+        <v>12.18046740212547</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>6.422779922824949</v>
+        <v>6.353717773117155</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1019546349309856</v>
+        <v>0.1015297361904689</v>
       </c>
       <c r="C95">
-        <v>112.2958345863838</v>
+        <v>111.0766409742188</v>
       </c>
       <c r="D95">
-        <v>353.7648345863838</v>
+        <v>355.9786409742188</v>
       </c>
       <c r="E95">
-        <v>92.76900000000001</v>
+        <v>96.20200000000006</v>
       </c>
       <c r="F95">
-        <v>319.269</v>
+        <v>322.7020000000001</v>
       </c>
       <c r="G95">
         <v>77.8</v>
@@ -9202,28 +9202,28 @@
         <v>110.15</v>
       </c>
       <c r="M95">
-        <v>17.3363067</v>
+        <v>17.5227186</v>
       </c>
       <c r="N95">
-        <v>92.81369330000001</v>
+        <v>92.6272814</v>
       </c>
       <c r="O95">
-        <v>31.55665572200001</v>
+        <v>31.493275676</v>
       </c>
       <c r="P95">
-        <v>61.25703757800001</v>
+        <v>61.134005724</v>
       </c>
       <c r="Q95">
-        <v>59.857037578</v>
+        <v>59.73400572399999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9803613561569381</v>
+        <v>1.130700269841149</v>
       </c>
       <c r="T95">
-        <v>12.18046740212547</v>
+        <v>14.13988742879087</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>6.353717773117155</v>
+        <v>6.286125030849949</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1015297361904689</v>
+        <v>0.1011048374499521</v>
       </c>
       <c r="C96">
-        <v>111.0766409742188</v>
+        <v>109.8853291677077</v>
       </c>
       <c r="D96">
-        <v>355.9786409742188</v>
+        <v>358.2203291677077</v>
       </c>
       <c r="E96">
-        <v>96.20200000000006</v>
+        <v>99.63500000000005</v>
       </c>
       <c r="F96">
-        <v>322.7020000000001</v>
+        <v>326.135</v>
       </c>
       <c r="G96">
         <v>77.8</v>
@@ -9284,28 +9284,28 @@
         <v>110.15</v>
       </c>
       <c r="M96">
-        <v>17.5227186</v>
+        <v>17.7091305</v>
       </c>
       <c r="N96">
-        <v>92.6272814</v>
+        <v>92.44086950000001</v>
       </c>
       <c r="O96">
-        <v>31.493275676</v>
+        <v>31.42989563</v>
       </c>
       <c r="P96">
-        <v>61.134005724</v>
+        <v>61.01097387</v>
       </c>
       <c r="Q96">
-        <v>59.73400572399999</v>
+        <v>59.61097387</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.130700269841149</v>
+        <v>1.341174748999044</v>
       </c>
       <c r="T96">
-        <v>14.13988742879087</v>
+        <v>16.88307546612244</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>6.286125030849949</v>
+        <v>6.219955293683108</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1011048374499521</v>
+        <v>0.1006799387094354</v>
       </c>
       <c r="C97">
-        <v>109.8853291677077</v>
+        <v>108.7224292413653</v>
       </c>
       <c r="D97">
-        <v>358.2203291677077</v>
+        <v>360.4904292413653</v>
       </c>
       <c r="E97">
-        <v>99.63500000000005</v>
+        <v>103.068</v>
       </c>
       <c r="F97">
-        <v>326.135</v>
+        <v>329.568</v>
       </c>
       <c r="G97">
         <v>77.8</v>
@@ -9366,28 +9366,28 @@
         <v>110.15</v>
       </c>
       <c r="M97">
-        <v>17.7091305</v>
+        <v>17.8955424</v>
       </c>
       <c r="N97">
-        <v>92.44086950000001</v>
+        <v>92.25445759999999</v>
       </c>
       <c r="O97">
-        <v>31.42989563</v>
+        <v>31.366515584</v>
       </c>
       <c r="P97">
-        <v>61.01097387</v>
+        <v>60.887942016</v>
       </c>
       <c r="Q97">
-        <v>59.61097387</v>
+        <v>59.48794201599999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.341174748999044</v>
+        <v>1.656886467735887</v>
       </c>
       <c r="T97">
-        <v>16.88307546612244</v>
+        <v>20.9978575221198</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>6.219955293683108</v>
+        <v>6.155164092707242</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1006799387094354</v>
+        <v>0.1008952399689186</v>
       </c>
       <c r="C98">
-        <v>108.7224292413654</v>
+        <v>104.1355581192419</v>
       </c>
       <c r="D98">
-        <v>360.4904292413653</v>
+        <v>359.3365581192419</v>
       </c>
       <c r="E98">
-        <v>103.068</v>
+        <v>106.501</v>
       </c>
       <c r="F98">
-        <v>329.568</v>
+        <v>333.001</v>
       </c>
       <c r="G98">
         <v>77.8</v>
@@ -9448,45 +9448,45 @@
         <v>110.15</v>
       </c>
       <c r="M98">
-        <v>17.8955424</v>
+        <v>18.4149553</v>
       </c>
       <c r="N98">
-        <v>92.25445760000001</v>
+        <v>91.7350447</v>
       </c>
       <c r="O98">
-        <v>31.36651558400001</v>
+        <v>31.189915198</v>
       </c>
       <c r="P98">
-        <v>60.887942016</v>
+        <v>60.54512950199999</v>
       </c>
       <c r="Q98">
-        <v>59.487942016</v>
+        <v>59.14512950199999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.656886467735883</v>
+        <v>2.183072665630619</v>
       </c>
       <c r="T98">
-        <v>20.99785752211974</v>
+        <v>27.85582761544864</v>
       </c>
       <c r="U98">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V98">
         <v>0.34</v>
       </c>
       <c r="W98">
-        <v>0.03583799999999999</v>
+        <v>0.036498</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y98">
-        <v>6.155164092707244</v>
+        <v>5.981551310091967</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1008952399689186</v>
+        <v>0.1004769412284019</v>
       </c>
       <c r="C99">
-        <v>104.1355581192419</v>
+        <v>102.9511682341451</v>
       </c>
       <c r="D99">
-        <v>359.3365581192419</v>
+        <v>361.5851682341451</v>
       </c>
       <c r="E99">
-        <v>106.501</v>
+        <v>109.934</v>
       </c>
       <c r="F99">
-        <v>333.001</v>
+        <v>336.434</v>
       </c>
       <c r="G99">
         <v>77.8</v>
@@ -9530,28 +9530,28 @@
         <v>110.15</v>
       </c>
       <c r="M99">
-        <v>18.4149553</v>
+        <v>18.6048002</v>
       </c>
       <c r="N99">
-        <v>91.7350447</v>
+        <v>91.54519980000001</v>
       </c>
       <c r="O99">
-        <v>31.189915198</v>
+        <v>31.125367932</v>
       </c>
       <c r="P99">
-        <v>60.54512950199999</v>
+        <v>60.419831868</v>
       </c>
       <c r="Q99">
-        <v>59.14512950199999</v>
+        <v>59.019831868</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.183072665630619</v>
+        <v>3.235445061420092</v>
       </c>
       <c r="T99">
-        <v>27.85582761544864</v>
+        <v>41.57176780210643</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>5.981551310091967</v>
+        <v>5.920515072233885</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1004769412284019</v>
+        <v>0.1000586424878852</v>
       </c>
       <c r="C100">
-        <v>102.9511682341451</v>
+        <v>101.7950976887354</v>
       </c>
       <c r="D100">
-        <v>361.5851682341451</v>
+        <v>363.8620976887354</v>
       </c>
       <c r="E100">
-        <v>109.934</v>
+        <v>113.367</v>
       </c>
       <c r="F100">
-        <v>336.434</v>
+        <v>339.867</v>
       </c>
       <c r="G100">
         <v>77.8</v>
@@ -9612,28 +9612,28 @@
         <v>110.15</v>
       </c>
       <c r="M100">
-        <v>18.6048002</v>
+        <v>18.7946451</v>
       </c>
       <c r="N100">
-        <v>91.54519980000001</v>
+        <v>91.35535490000001</v>
       </c>
       <c r="O100">
-        <v>31.125367932</v>
+        <v>31.06082066600001</v>
       </c>
       <c r="P100">
-        <v>60.419831868</v>
+        <v>60.294534234</v>
       </c>
       <c r="Q100">
-        <v>59.019831868</v>
+        <v>58.894534234</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.235445061420092</v>
+        <v>6.392562248788509</v>
       </c>
       <c r="T100">
-        <v>41.57176780210643</v>
+        <v>82.71958836207979</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>5.920515072233885</v>
+        <v>5.860711889686068</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1000586424878852</v>
-      </c>
-      <c r="C101">
-        <v>101.7950976887354</v>
-      </c>
-      <c r="D101">
-        <v>363.8620976887354</v>
-      </c>
-      <c r="E101">
-        <v>113.367</v>
-      </c>
-      <c r="F101">
-        <v>339.867</v>
-      </c>
-      <c r="G101">
-        <v>77.8</v>
-      </c>
-      <c r="H101">
-        <v>116.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>108.75</v>
-      </c>
-      <c r="K101">
-        <v>-1.400000000000006</v>
-      </c>
-      <c r="L101">
-        <v>110.15</v>
-      </c>
-      <c r="M101">
-        <v>18.7946451</v>
-      </c>
-      <c r="N101">
-        <v>91.35535490000001</v>
-      </c>
-      <c r="O101">
-        <v>31.06082066600001</v>
-      </c>
-      <c r="P101">
-        <v>60.294534234</v>
-      </c>
-      <c r="Q101">
-        <v>58.894534234</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.392562248788509</v>
-      </c>
-      <c r="T101">
-        <v>82.71958836207979</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.34</v>
-      </c>
-      <c r="W101">
-        <v>0.036498</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>5.860711889686068</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
